--- a/aranceles.xlsx
+++ b/aranceles.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Policlinico Tabancura\Toma_Muestra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EQUIPO\Desktop\Sandbox\dev\cotizador-examenes\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBECD1F-E675-4E7C-9B0F-4C2F174CCF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aranceles" sheetId="2" r:id="rId1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="526">
   <si>
     <t>Codigo Ingreso</t>
   </si>
@@ -1609,12 +1610,15 @@
   </si>
   <si>
     <t>VALOR PARTICULAR General</t>
+  </si>
+  <si>
+    <t>Tubo glucosa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1696,7 +1700,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="LISTA COMPLETA"/>
@@ -1992,19 +1996,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F387"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F388"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="107.88671875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="6"/>
+    <col min="1" max="1" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="107.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2024,7 +2028,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>302005</v>
       </c>
@@ -2044,7 +2048,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>302101</v>
       </c>
@@ -2064,7 +2068,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>302013</v>
       </c>
@@ -2084,7 +2088,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>302012</v>
       </c>
@@ -2104,7 +2108,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>302015</v>
       </c>
@@ -2124,7 +2128,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>302068</v>
       </c>
@@ -2144,7 +2148,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>302067</v>
       </c>
@@ -2164,7 +2168,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>302023</v>
       </c>
@@ -2184,7 +2188,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>302048</v>
       </c>
@@ -2204,7 +2208,7 @@
         <v>8372</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>302040</v>
       </c>
@@ -2224,7 +2228,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>302042</v>
       </c>
@@ -2244,7 +2248,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>302045</v>
       </c>
@@ -2264,7 +2268,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>302047</v>
       </c>
@@ -2284,7 +2288,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>301041</v>
       </c>
@@ -2304,7 +2308,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>241</v>
       </c>
@@ -2324,7 +2328,7 @@
         <v>8474</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>302030</v>
       </c>
@@ -2344,7 +2348,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>302057</v>
       </c>
@@ -2364,7 +2368,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>302075</v>
       </c>
@@ -2384,7 +2388,7 @@
         <v>12566</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>302076</v>
       </c>
@@ -2404,7 +2408,7 @@
         <v>14726</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>302034</v>
       </c>
@@ -2424,7 +2428,7 @@
         <v>8952</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>305031</v>
       </c>
@@ -2444,7 +2448,7 @@
         <v>8756</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>405</v>
       </c>
@@ -2464,7 +2468,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>302100</v>
       </c>
@@ -2484,7 +2488,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>302063</v>
       </c>
@@ -2504,7 +2508,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>302064</v>
       </c>
@@ -2524,7 +2528,7 @@
         <v>2544</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>422</v>
       </c>
@@ -2544,7 +2548,7 @@
         <v>4577</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>302024</v>
       </c>
@@ -2564,7 +2568,7 @@
         <v>4240</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>309010</v>
       </c>
@@ -2584,7 +2588,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>309013</v>
       </c>
@@ -2604,7 +2608,7 @@
         <v>4088</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>305070</v>
       </c>
@@ -2624,7 +2628,7 @@
         <v>13111</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>303031</v>
       </c>
@@ -2644,7 +2648,7 @@
         <v>19867</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>303030</v>
       </c>
@@ -2664,7 +2668,7 @@
         <v>7765</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>303015</v>
       </c>
@@ -2684,7 +2688,7 @@
         <v>7907</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>303024</v>
       </c>
@@ -2704,7 +2708,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>303017</v>
       </c>
@@ -2724,7 +2728,7 @@
         <v>7372</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>303026</v>
       </c>
@@ -2744,7 +2748,7 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>303027</v>
       </c>
@@ -2764,7 +2768,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>303028</v>
       </c>
@@ -2784,7 +2788,7 @@
         <v>6765</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>306169</v>
       </c>
@@ -2804,7 +2808,7 @@
         <v>7783</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>302077</v>
       </c>
@@ -2824,7 +2828,7 @@
         <v>10907</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>302078</v>
       </c>
@@ -2844,7 +2848,7 @@
         <v>24249</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>309022</v>
       </c>
@@ -2864,7 +2868,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>306034</v>
       </c>
@@ -2884,7 +2888,7 @@
         <v>7810</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>306007</v>
       </c>
@@ -2904,7 +2908,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>306008</v>
       </c>
@@ -2924,7 +2928,7 @@
         <v>5230</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>306016</v>
       </c>
@@ -2944,7 +2948,7 @@
         <v>4266</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>308044</v>
       </c>
@@ -2964,7 +2968,7 @@
         <v>11210</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>308004</v>
       </c>
@@ -2984,7 +2988,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>308063</v>
       </c>
@@ -3004,7 +3008,7 @@
         <v>29680</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>309024</v>
       </c>
@@ -3024,7 +3028,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>306099</v>
       </c>
@@ -3044,7 +3048,7 @@
         <v>15603</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>306005</v>
       </c>
@@ -3064,7 +3068,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>306011</v>
       </c>
@@ -3084,7 +3088,7 @@
         <v>5328</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>306023</v>
       </c>
@@ -3104,7 +3108,7 @@
         <v>9086</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>306038</v>
       </c>
@@ -3124,7 +3128,7 @@
         <v>3883</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>306079</v>
       </c>
@@ -3144,7 +3148,7 @@
         <v>7881</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>306081</v>
       </c>
@@ -3164,7 +3168,7 @@
         <v>12040</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>306056</v>
       </c>
@@ -3184,7 +3188,7 @@
         <v>5730</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>308005</v>
       </c>
@@ -3204,7 +3208,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>306051</v>
       </c>
@@ -3224,7 +3228,7 @@
         <v>3026</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>308013</v>
       </c>
@@ -3244,7 +3248,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>301036</v>
       </c>
@@ -3264,7 +3268,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>301038</v>
       </c>
@@ -3284,7 +3288,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>301045</v>
       </c>
@@ -3304,7 +3308,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>301062</v>
       </c>
@@ -3324,7 +3328,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>301063</v>
       </c>
@@ -3344,7 +3348,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>301065</v>
       </c>
@@ -3364,7 +3368,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>301067</v>
       </c>
@@ -3384,7 +3388,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>301064</v>
       </c>
@@ -3404,7 +3408,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>301066</v>
       </c>
@@ -3424,7 +3428,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>301068</v>
       </c>
@@ -3444,7 +3448,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>301086</v>
       </c>
@@ -3464,7 +3468,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>301059</v>
       </c>
@@ -3484,7 +3488,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>301072</v>
       </c>
@@ -3504,7 +3508,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>301085</v>
       </c>
@@ -3524,7 +3528,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>4</v>
       </c>
@@ -3544,7 +3548,7 @@
         <v>62885</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>303029</v>
       </c>
@@ -3564,7 +3568,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
@@ -3584,7 +3588,7 @@
         <v>43472</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>10</v>
       </c>
@@ -3604,7 +3608,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>305086</v>
       </c>
@@ -3624,7 +3628,7 @@
         <v>15235</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>12</v>
       </c>
@@ -3644,7 +3648,7 @@
         <v>134581</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>301002</v>
       </c>
@@ -3664,7 +3668,7 @@
         <v>7211</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>302035</v>
       </c>
@@ -3684,7 +3688,7 @@
         <v>8996</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3704,7 +3708,7 @@
         <v>15140</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>19</v>
       </c>
@@ -3724,7 +3728,7 @@
         <v>15140</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>302050</v>
       </c>
@@ -3744,7 +3748,7 @@
         <v>7658</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>306069</v>
       </c>
@@ -3764,7 +3768,7 @@
         <v>8978</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>24</v>
       </c>
@@ -3784,7 +3788,7 @@
         <v>9063</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>303002</v>
       </c>
@@ -3804,7 +3808,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>305001</v>
       </c>
@@ -3824,7 +3828,7 @@
         <v>7729</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>305003</v>
       </c>
@@ -3844,7 +3848,7 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>28</v>
       </c>
@@ -3864,7 +3868,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>309006</v>
       </c>
@@ -3884,7 +3888,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>302008</v>
       </c>
@@ -3904,7 +3908,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>32</v>
       </c>
@@ -3924,7 +3928,7 @@
         <v>66263</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>35</v>
       </c>
@@ -3944,7 +3948,7 @@
         <v>66263</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>38</v>
       </c>
@@ -3964,7 +3968,7 @@
         <v>79651</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>303003</v>
       </c>
@@ -3984,7 +3988,7 @@
         <v>8042</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>305105</v>
       </c>
@@ -4004,7 +4008,7 @@
         <v>40565</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>305007</v>
       </c>
@@ -4024,7 +4028,7 @@
         <v>8711</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>305005</v>
       </c>
@@ -4044,7 +4048,7 @@
         <v>10907</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>305082</v>
       </c>
@@ -4064,7 +4068,7 @@
         <v>23366</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>305081</v>
       </c>
@@ -4084,7 +4088,7 @@
         <v>16333</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>305108</v>
       </c>
@@ -4104,7 +4108,7 @@
         <v>22913</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>305085</v>
       </c>
@@ -4124,7 +4128,7 @@
         <v>33174</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>305124</v>
       </c>
@@ -4144,7 +4148,7 @@
         <v>37142</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>306041</v>
       </c>
@@ -4164,7 +4168,7 @@
         <v>7167</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>305004</v>
       </c>
@@ -4184,7 +4188,7 @@
         <v>15512</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>48</v>
       </c>
@@ -4204,7 +4208,7 @@
         <v>75290</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>49</v>
       </c>
@@ -4224,7 +4228,7 @@
         <v>75290</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>305008</v>
       </c>
@@ -4244,7 +4248,7 @@
         <v>6739</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>305009</v>
       </c>
@@ -4264,7 +4268,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>56</v>
       </c>
@@ -4284,7 +4288,7 @@
         <v>185578</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>59</v>
       </c>
@@ -4304,7 +4308,7 @@
         <v>241367</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>63</v>
       </c>
@@ -4324,7 +4328,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>301008</v>
       </c>
@@ -4344,7 +4348,7 @@
         <v>7542</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>302070</v>
       </c>
@@ -4364,7 +4368,7 @@
         <v>9969</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>68</v>
       </c>
@@ -4384,7 +4388,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>309034</v>
       </c>
@@ -4404,7 +4408,7 @@
         <v>50894</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>71</v>
       </c>
@@ -4424,7 +4428,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>202232</v>
       </c>
@@ -4444,7 +4448,7 @@
         <v>42846</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>202233</v>
       </c>
@@ -4464,7 +4468,7 @@
         <v>42846</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>74</v>
       </c>
@@ -4484,7 +4488,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>76</v>
       </c>
@@ -4504,7 +4508,7 @@
         <v>26473</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>305010</v>
       </c>
@@ -4524,7 +4528,7 @@
         <v>11585</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>306118</v>
       </c>
@@ -4544,7 +4548,7 @@
         <v>68641</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>306013</v>
       </c>
@@ -4564,7 +4568,7 @@
         <v>10112</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>81</v>
       </c>
@@ -4584,7 +4588,7 @@
         <v>15659</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>82</v>
       </c>
@@ -4604,7 +4608,7 @@
         <v>15659</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>306033</v>
       </c>
@@ -4624,7 +4628,7 @@
         <v>2981</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>305170</v>
       </c>
@@ -4644,7 +4648,7 @@
         <v>13584</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>85</v>
       </c>
@@ -4664,7 +4668,7 @@
         <v>154672</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>87</v>
       </c>
@@ -4684,7 +4688,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>89</v>
       </c>
@@ -4704,7 +4708,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>309008</v>
       </c>
@@ -4724,7 +4728,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>308049</v>
       </c>
@@ -4744,7 +4748,7 @@
         <v>46378</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>94</v>
       </c>
@@ -4764,7 +4768,7 @@
         <v>73377</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>96</v>
       </c>
@@ -4784,7 +4788,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>301029</v>
       </c>
@@ -4804,7 +4808,7 @@
         <v>6658</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>305084</v>
       </c>
@@ -4824,7 +4828,7 @@
         <v>18564</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>306084</v>
       </c>
@@ -4844,7 +4848,7 @@
         <v>122309</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>306085</v>
       </c>
@@ -4864,7 +4868,7 @@
         <v>136092</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>302017</v>
       </c>
@@ -4884,7 +4888,7 @@
         <v>3186</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>303051</v>
       </c>
@@ -4904,7 +4908,7 @@
         <v>52435</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>302019</v>
       </c>
@@ -4924,7 +4928,7 @@
         <v>5311</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>101</v>
       </c>
@@ -4944,7 +4948,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>306061</v>
       </c>
@@ -4964,7 +4968,7 @@
         <v>8086</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>103</v>
       </c>
@@ -4984,7 +4988,7 @@
         <v>74020</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>306097</v>
       </c>
@@ -5004,7 +5008,7 @@
         <v>42884</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>106</v>
       </c>
@@ -5024,7 +5028,7 @@
         <v>29601</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>306182</v>
       </c>
@@ -5044,7 +5048,7 @@
         <v>106975</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>109</v>
       </c>
@@ -5064,7 +5068,7 @@
         <v>129505</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>202242</v>
       </c>
@@ -5084,7 +5088,7 @@
         <v>23541</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>309012</v>
       </c>
@@ -5104,7 +5108,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>302032</v>
       </c>
@@ -5124,7 +5128,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>115</v>
       </c>
@@ -5144,7 +5148,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>117</v>
       </c>
@@ -5164,7 +5168,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>309036</v>
       </c>
@@ -5184,7 +5188,7 @@
         <v>50423</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>302020</v>
       </c>
@@ -5204,7 +5208,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>302021</v>
       </c>
@@ -5224,7 +5228,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>305012</v>
       </c>
@@ -5244,7 +5248,7 @@
         <v>6739</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>127</v>
       </c>
@@ -5264,7 +5268,7 @@
         <v>62885</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>303035</v>
       </c>
@@ -5284,7 +5288,7 @@
         <v>8158</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>303056</v>
       </c>
@@ -5304,7 +5308,7 @@
         <v>49420</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>303006</v>
       </c>
@@ -5324,7 +5328,7 @@
         <v>8042</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>132</v>
       </c>
@@ -5344,7 +5348,7 @@
         <v>62885</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>302025</v>
       </c>
@@ -5364,7 +5368,7 @@
         <v>7640</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>302026</v>
       </c>
@@ -5384,7 +5388,7 @@
         <v>5471</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>139</v>
       </c>
@@ -5404,7 +5408,7 @@
         <v>115436</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>141</v>
       </c>
@@ -5424,7 +5428,7 @@
         <v>274739</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>143</v>
       </c>
@@ -5444,7 +5448,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>145</v>
       </c>
@@ -5464,7 +5468,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>303008</v>
       </c>
@@ -5484,7 +5488,7 @@
         <v>10041</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>155</v>
       </c>
@@ -5504,7 +5508,7 @@
         <v>296153</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>801001</v>
       </c>
@@ -5524,7 +5528,7 @@
         <v>9978</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>159</v>
       </c>
@@ -5544,7 +5548,7 @@
         <v>31460</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>308007</v>
       </c>
@@ -5564,7 +5568,7 @@
         <v>82960</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>302061</v>
       </c>
@@ -5584,7 +5588,7 @@
         <v>9050</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>308019</v>
       </c>
@@ -5604,7 +5608,7 @@
         <v>9586</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>167</v>
       </c>
@@ -5624,7 +5628,7 @@
         <v>50873</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>169</v>
       </c>
@@ -5644,7 +5648,7 @@
         <v>60114</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>302033</v>
       </c>
@@ -5664,7 +5668,7 @@
         <v>11469</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>173</v>
       </c>
@@ -5684,7 +5688,7 @@
         <v>104069</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>306087</v>
       </c>
@@ -5704,7 +5708,7 @@
         <v>159094</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>303009</v>
       </c>
@@ -5724,7 +5728,7 @@
         <v>8452</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>176</v>
       </c>
@@ -5744,7 +5748,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>308047</v>
       </c>
@@ -5764,7 +5768,7 @@
         <v>69590</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>180</v>
       </c>
@@ -5784,7 +5788,7 @@
         <v>6310</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>181</v>
       </c>
@@ -5804,7 +5808,7 @@
         <v>11548</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>183</v>
       </c>
@@ -5824,7 +5828,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>185</v>
       </c>
@@ -5844,7 +5848,7 @@
         <v>2113514</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>188</v>
       </c>
@@ -5864,7 +5868,7 @@
         <v>76309</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>190</v>
       </c>
@@ -5884,7 +5888,7 @@
         <v>82815</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>305020</v>
       </c>
@@ -5904,7 +5908,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>301025</v>
       </c>
@@ -5924,7 +5928,7 @@
         <v>7283</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>301089</v>
       </c>
@@ -5944,7 +5948,7 @@
         <v>14495</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>196</v>
       </c>
@@ -5964,7 +5968,7 @@
         <v>76309</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>301026</v>
       </c>
@@ -5984,7 +5988,7 @@
         <v>8657</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>309015</v>
       </c>
@@ -6004,7 +6008,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>205</v>
       </c>
@@ -6024,7 +6028,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>210</v>
       </c>
@@ -6044,7 +6048,7 @@
         <v>34589</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>303012</v>
       </c>
@@ -6064,7 +6068,7 @@
         <v>10799</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>213</v>
       </c>
@@ -6084,7 +6088,7 @@
         <v>459872</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>301017</v>
       </c>
@@ -6104,7 +6108,7 @@
         <v>6881</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>309016</v>
       </c>
@@ -6124,7 +6128,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>303014</v>
       </c>
@@ -6144,7 +6148,7 @@
         <v>7738</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>220</v>
       </c>
@@ -6164,7 +6168,7 @@
         <v>67085</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>301035</v>
       </c>
@@ -6184,7 +6188,7 @@
         <v>6854</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>202215</v>
       </c>
@@ -6204,7 +6208,7 @@
         <v>49263</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>202249</v>
       </c>
@@ -6224,7 +6228,7 @@
         <v>73377</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>225</v>
       </c>
@@ -6244,7 +6248,7 @@
         <v>359855</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>301044</v>
       </c>
@@ -6264,7 +6268,7 @@
         <v>7622</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>306074</v>
       </c>
@@ -6284,7 +6288,7 @@
         <v>11023</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>306075</v>
       </c>
@@ -6304,7 +6308,7 @@
         <v>10799</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>306080</v>
       </c>
@@ -6324,7 +6328,7 @@
         <v>10978</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>306076</v>
       </c>
@@ -6344,7 +6348,7 @@
         <v>11040</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>306078</v>
       </c>
@@ -6364,7 +6368,7 @@
         <v>9978</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>232</v>
       </c>
@@ -6384,7 +6388,7 @@
         <v>107786</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>235</v>
       </c>
@@ -6404,7 +6408,7 @@
         <v>62867</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>236</v>
       </c>
@@ -6424,7 +6428,7 @@
         <v>123517</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>309017</v>
       </c>
@@ -6444,7 +6448,7 @@
         <v>6658</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>301028</v>
       </c>
@@ -6464,7 +6468,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>303058</v>
       </c>
@@ -6484,7 +6488,7 @@
         <v>50219</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>303007</v>
       </c>
@@ -6504,7 +6508,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>303016</v>
       </c>
@@ -6524,7 +6528,7 @@
         <v>7925</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>303018</v>
       </c>
@@ -6544,7 +6548,7 @@
         <v>12067</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>303048</v>
       </c>
@@ -6564,7 +6568,7 @@
         <v>19349</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>303123</v>
       </c>
@@ -6584,7 +6588,7 @@
         <v>18617</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>249</v>
       </c>
@@ -6604,7 +6608,7 @@
         <v>64778</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>305025</v>
       </c>
@@ -6624,7 +6628,7 @@
         <v>13397</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>305027</v>
       </c>
@@ -6644,7 +6648,7 @@
         <v>7408</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
         <v>305028</v>
       </c>
@@ -6664,7 +6668,7 @@
         <v>7729</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>305029</v>
       </c>
@@ -6684,7 +6688,7 @@
         <v>7595</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>202260</v>
       </c>
@@ -6704,7 +6708,7 @@
         <v>108019</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>303047</v>
       </c>
@@ -6724,7 +6728,7 @@
         <v>19653</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>256</v>
       </c>
@@ -6744,7 +6748,7 @@
         <v>33588</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>302039</v>
       </c>
@@ -6764,7 +6768,7 @@
         <v>9113</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>302031</v>
       </c>
@@ -6784,7 +6788,7 @@
         <v>9452</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>258</v>
       </c>
@@ -6804,7 +6808,7 @@
         <v>76309</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>302004</v>
       </c>
@@ -6824,7 +6828,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>309007</v>
       </c>
@@ -6844,7 +6848,7 @@
         <v>8399</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>261</v>
       </c>
@@ -6864,7 +6868,7 @@
         <v>67085</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>305089</v>
       </c>
@@ -6884,7 +6888,7 @@
         <v>65831</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>305092</v>
       </c>
@@ -6904,7 +6908,7 @@
         <v>40895</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>305091</v>
       </c>
@@ -6924,7 +6928,7 @@
         <v>42001</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>302053</v>
       </c>
@@ -6944,7 +6948,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>267</v>
       </c>
@@ -6964,7 +6968,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
         <v>269</v>
       </c>
@@ -6984,7 +6988,7 @@
         <v>67353</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>302055</v>
       </c>
@@ -7004,7 +7008,7 @@
         <v>4195</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>272</v>
       </c>
@@ -7024,7 +7028,7 @@
         <v>2985</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>302056</v>
       </c>
@@ -7044,7 +7048,7 @@
         <v>4588</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
         <v>275</v>
       </c>
@@ -7064,7 +7068,7 @@
         <v>121586</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>277</v>
       </c>
@@ -7084,7 +7088,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
         <v>279</v>
       </c>
@@ -7104,7 +7108,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>281</v>
       </c>
@@ -7124,7 +7128,7 @@
         <v>108698</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
         <v>303050</v>
       </c>
@@ -7144,7 +7148,7 @@
         <v>60994</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>306070</v>
       </c>
@@ -7164,7 +7168,7 @@
         <v>8042</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
         <v>305107</v>
       </c>
@@ -7184,7 +7188,7 @@
         <v>39922</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
         <v>306036</v>
       </c>
@@ -7204,7 +7208,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
         <v>286</v>
       </c>
@@ -7224,7 +7228,7 @@
         <v>134134</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
         <v>288</v>
       </c>
@@ -7244,7 +7248,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
         <v>290</v>
       </c>
@@ -7264,7 +7268,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>292</v>
       </c>
@@ -7284,7 +7288,7 @@
         <v>74020</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
         <v>306037</v>
       </c>
@@ -7304,7 +7308,7 @@
         <v>7515</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>296</v>
       </c>
@@ -7324,7 +7328,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
         <v>309020</v>
       </c>
@@ -7344,7 +7348,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
         <v>301</v>
       </c>
@@ -7364,7 +7368,7 @@
         <v>12137</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="3">
         <v>309025</v>
       </c>
@@ -7384,7 +7388,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
         <v>202258</v>
       </c>
@@ -7404,7 +7408,7 @@
         <v>23541</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="3">
         <v>202258</v>
       </c>
@@ -7424,7 +7428,7 @@
         <v>23541</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>307</v>
       </c>
@@ -7444,7 +7448,7 @@
         <v>144001</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="3">
         <v>202329</v>
       </c>
@@ -7464,7 +7468,7 @@
         <v>98099</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>310</v>
       </c>
@@ -7484,7 +7488,7 @@
         <v>54947</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>312</v>
       </c>
@@ -7504,7 +7508,7 @@
         <v>83262</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>314</v>
       </c>
@@ -7524,7 +7528,7 @@
         <v>141713</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
         <v>316</v>
       </c>
@@ -7544,7 +7548,7 @@
         <v>107858</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>318</v>
       </c>
@@ -7564,7 +7568,7 @@
         <v>43955</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="3">
         <v>202216</v>
       </c>
@@ -7584,7 +7588,7 @@
         <v>39307</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>321</v>
       </c>
@@ -7604,7 +7608,7 @@
         <v>157211</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="3">
         <v>202319</v>
       </c>
@@ -7624,7 +7628,7 @@
         <v>174407</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>324</v>
       </c>
@@ -7644,7 +7648,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
         <v>326</v>
       </c>
@@ -7664,7 +7668,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>328</v>
       </c>
@@ -7684,7 +7688,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>330</v>
       </c>
@@ -7704,7 +7708,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
         <v>332</v>
       </c>
@@ -7724,7 +7728,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
         <v>334</v>
       </c>
@@ -7744,7 +7748,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>336</v>
       </c>
@@ -7764,7 +7768,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>338</v>
       </c>
@@ -7784,7 +7788,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>340</v>
       </c>
@@ -7804,7 +7808,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
         <v>342</v>
       </c>
@@ -7824,7 +7828,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>344</v>
       </c>
@@ -7844,7 +7848,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
         <v>346</v>
       </c>
@@ -7864,7 +7868,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>348</v>
       </c>
@@ -7884,7 +7888,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
         <v>350</v>
       </c>
@@ -7904,7 +7908,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>352</v>
       </c>
@@ -7924,7 +7928,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
         <v>354</v>
       </c>
@@ -7944,7 +7948,7 @@
         <v>95582</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>356</v>
       </c>
@@ -7964,7 +7968,7 @@
         <v>130792</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
         <v>358</v>
       </c>
@@ -7984,7 +7988,7 @@
         <v>367362</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>360</v>
       </c>
@@ -8004,7 +8008,7 @@
         <v>295080</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
         <v>362</v>
       </c>
@@ -8024,7 +8028,7 @@
         <v>76755</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>363</v>
       </c>
@@ -8044,7 +8048,7 @@
         <v>109412</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
         <v>364</v>
       </c>
@@ -8064,7 +8068,7 @@
         <v>115562</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>366</v>
       </c>
@@ -8084,7 +8088,7 @@
         <v>71231</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
         <v>368</v>
       </c>
@@ -8104,7 +8108,7 @@
         <v>138763</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="3">
         <v>202313</v>
       </c>
@@ -8124,7 +8128,7 @@
         <v>113310</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
         <v>371</v>
       </c>
@@ -8144,7 +8148,7 @@
         <v>141641</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="3">
         <v>202315</v>
       </c>
@@ -8164,7 +8168,7 @@
         <v>57808</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A309" s="3">
         <v>306122</v>
       </c>
@@ -8184,7 +8188,7 @@
         <v>86822</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
         <v>202326</v>
       </c>
@@ -8204,7 +8208,7 @@
         <v>98099</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>377</v>
       </c>
@@ -8224,7 +8228,7 @@
         <v>444812</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="3">
         <v>303052</v>
       </c>
@@ -8244,7 +8248,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="3">
         <v>305099</v>
       </c>
@@ -8264,7 +8268,7 @@
         <v>38305</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="3">
         <v>303055</v>
       </c>
@@ -8284,7 +8288,7 @@
         <v>57663</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
         <v>383</v>
       </c>
@@ -8304,7 +8308,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
         <v>385</v>
       </c>
@@ -8324,7 +8328,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="3">
         <v>302084</v>
       </c>
@@ -8344,7 +8348,7 @@
         <v>65063</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
         <v>309027</v>
       </c>
@@ -8364,7 +8368,7 @@
         <v>3731</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
         <v>389</v>
       </c>
@@ -8384,7 +8388,7 @@
         <v>96953</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>391</v>
       </c>
@@ -8404,7 +8408,7 @@
         <v>96953</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
         <v>393</v>
       </c>
@@ -8424,7 +8428,7 @@
         <v>450542</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
         <v>302085</v>
       </c>
@@ -8444,7 +8448,7 @@
         <v>32805</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="3">
         <v>301096</v>
       </c>
@@ -8464,7 +8468,7 @@
         <v>47060</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
         <v>303019</v>
       </c>
@@ -8484,7 +8488,7 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="3">
         <v>303020</v>
       </c>
@@ -8504,7 +8508,7 @@
         <v>7907</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="3">
         <v>202424</v>
       </c>
@@ -8524,7 +8528,7 @@
         <v>28439</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="3">
         <v>202338</v>
       </c>
@@ -8544,7 +8548,7 @@
         <v>138763</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="3">
         <v>301093</v>
       </c>
@@ -8564,7 +8568,7 @@
         <v>33433</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="3">
         <v>301092</v>
       </c>
@@ -8584,7 +8588,7 @@
         <v>53077</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="3">
         <v>309028</v>
       </c>
@@ -8604,7 +8608,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A331" s="3">
         <v>306082</v>
       </c>
@@ -8624,7 +8628,7 @@
         <v>25253</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="3">
         <v>202347</v>
       </c>
@@ -8644,7 +8648,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="3">
         <v>303046</v>
       </c>
@@ -8664,7 +8668,7 @@
         <v>18234</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="3">
         <v>306099</v>
       </c>
@@ -8684,7 +8688,7 @@
         <v>15603</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
         <v>430</v>
       </c>
@@ -8704,7 +8708,7 @@
         <v>67085</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
         <v>432</v>
       </c>
@@ -8724,7 +8728,7 @@
         <v>110182</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
         <v>434</v>
       </c>
@@ -8744,7 +8748,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
         <v>438</v>
       </c>
@@ -8764,7 +8768,7 @@
         <v>274649</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>440</v>
       </c>
@@ -8784,7 +8788,7 @@
         <v>66138</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="3">
         <v>303023</v>
       </c>
@@ -8804,7 +8808,7 @@
         <v>9398</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="3">
         <v>303022</v>
       </c>
@@ -8824,7 +8828,7 @@
         <v>8229</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="3">
         <v>305118</v>
       </c>
@@ -8844,7 +8848,7 @@
         <v>91902</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="3">
         <v>305121</v>
       </c>
@@ -8864,7 +8868,7 @@
         <v>162668</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="3">
         <v>303025</v>
       </c>
@@ -8884,7 +8888,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="3">
         <v>202335</v>
       </c>
@@ -8904,7 +8908,7 @@
         <v>83065</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="3">
         <v>301082</v>
       </c>
@@ -8924,7 +8928,7 @@
         <v>7907</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="3">
         <v>305181</v>
       </c>
@@ -8944,7 +8948,7 @@
         <v>17466</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>457</v>
       </c>
@@ -8964,7 +8968,7 @@
         <v>78597</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
         <v>459</v>
       </c>
@@ -8984,7 +8988,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
         <v>202344</v>
       </c>
@@ -9004,7 +9008,7 @@
         <v>101423</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="3">
         <v>303057</v>
       </c>
@@ -9024,7 +9028,7 @@
         <v>21397</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
         <v>302027</v>
       </c>
@@ -9044,7 +9048,7 @@
         <v>16351</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
         <v>467</v>
       </c>
@@ -9064,7 +9068,7 @@
         <v>55502</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>469</v>
       </c>
@@ -9084,7 +9088,7 @@
         <v>55502</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
         <v>471</v>
       </c>
@@ -9104,7 +9108,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
         <v>309004</v>
       </c>
@@ -9124,7 +9128,7 @@
         <v>3186</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="3">
         <v>306042</v>
       </c>
@@ -9144,7 +9148,7 @@
         <v>4454</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>478</v>
       </c>
@@ -9164,7 +9168,7 @@
         <v>109234</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
         <v>480</v>
       </c>
@@ -9184,7 +9188,7 @@
         <v>141695</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>489</v>
       </c>
@@ -9204,7 +9208,7 @@
         <v>113346</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="3">
         <v>306111</v>
       </c>
@@ -9224,7 +9228,7 @@
         <v>77855</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A362" s="3">
         <v>306123</v>
       </c>
@@ -9244,7 +9248,7 @@
         <v>39485</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
         <v>492</v>
       </c>
@@ -9264,7 +9268,7 @@
         <v>46815</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="3">
         <v>302080</v>
       </c>
@@ -9284,7 +9288,7 @@
         <v>74497</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
         <v>496</v>
       </c>
@@ -9304,7 +9308,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>498</v>
       </c>
@@ -9324,7 +9328,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="3">
         <v>202270</v>
       </c>
@@ -9344,7 +9348,7 @@
         <v>17231</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="3">
         <v>202270</v>
       </c>
@@ -9364,7 +9368,7 @@
         <v>17231</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="3">
         <v>202225</v>
       </c>
@@ -9384,7 +9388,7 @@
         <v>71557</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
         <v>309029</v>
       </c>
@@ -9404,7 +9408,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="3">
         <v>306002</v>
       </c>
@@ -9424,7 +9428,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="3">
         <v>306017</v>
       </c>
@@ -9444,7 +9448,7 @@
         <v>3874</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="3">
         <v>306018</v>
       </c>
@@ -9464,7 +9468,7 @@
         <v>6596</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="3">
         <v>306004</v>
       </c>
@@ -9484,7 +9488,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A375" s="3">
         <v>306059</v>
       </c>
@@ -9504,7 +9508,7 @@
         <v>5694</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="3">
         <v>306039</v>
       </c>
@@ -9524,7 +9528,7 @@
         <v>5114</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="3">
         <v>306170</v>
       </c>
@@ -9544,7 +9548,7 @@
         <v>7372</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="3">
         <v>306098</v>
       </c>
@@ -9564,7 +9568,7 @@
         <v>19599</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="3">
         <v>301007</v>
       </c>
@@ -9584,7 +9588,7 @@
         <v>7542</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="3">
         <v>301014</v>
       </c>
@@ -9604,7 +9608,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="3">
         <v>702207</v>
       </c>
@@ -9624,7 +9628,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="3">
         <v>305035</v>
       </c>
@@ -9644,7 +9648,7 @@
         <v>3829</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="3">
         <v>301095</v>
       </c>
@@ -9664,7 +9668,7 @@
         <v>17234</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="3">
         <v>301021</v>
       </c>
@@ -9684,7 +9688,7 @@
         <v>3668</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="3">
         <v>301034</v>
       </c>
@@ -9704,7 +9708,7 @@
         <v>3597</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="3">
         <v>307011</v>
       </c>
@@ -9724,7 +9728,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="3">
         <v>307012</v>
       </c>
@@ -9744,8 +9748,28 @@
         <v>1169</v>
       </c>
     </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A388" s="3">
+        <v>222222222</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C388" s="5">
+        <v>5</v>
+      </c>
+      <c r="D388" s="5">
+        <v>5</v>
+      </c>
+      <c r="E388" s="5">
+        <v>5</v>
+      </c>
+      <c r="F388" s="5">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F387"/>
+  <autoFilter ref="A1:F387" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/aranceles.xlsx
+++ b/aranceles.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EQUIPO\Desktop\Sandbox\dev\cotizador-examenes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polic\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBECD1F-E675-4E7C-9B0F-4C2F174CCF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Aranceles" sheetId="2" r:id="rId1"/>
@@ -19,13 +18,13 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Aranceles!$A$1:$F$387</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Aranceles!$A$1:$F$388</definedName>
     <definedName name="_xlnm.Extract" localSheetId="0">Aranceles!$A$1:$B$1</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="0">Aranceles!#REF!</definedName>
     <definedName name="Ir" localSheetId="0">'[1]ESTUDIOS GENÉTICOS'!#REF!</definedName>
     <definedName name="Ir">'[1]ESTUDIOS GENÉTICOS'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913" calcMode="manual"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1618,7 +1617,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1700,7 +1699,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="LISTA COMPLETA"/>
@@ -1996,19 +1995,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F388"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="107.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.5703125" style="6"/>
+    <col min="1" max="1" width="12.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>302005</v>
       </c>
@@ -2036,10 +2035,10 @@
         <v>16</v>
       </c>
       <c r="C2" s="5">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="D2" s="5">
-        <v>1680</v>
+        <v>1720</v>
       </c>
       <c r="E2" s="5">
         <v>2916</v>
@@ -2048,7 +2047,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>302101</v>
       </c>
@@ -2056,10 +2055,10 @@
         <v>22</v>
       </c>
       <c r="C3" s="5">
-        <v>2370</v>
+        <v>2420</v>
       </c>
       <c r="D3" s="5">
-        <v>1630</v>
+        <v>1660</v>
       </c>
       <c r="E3" s="5">
         <v>2820</v>
@@ -2068,7 +2067,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>302013</v>
       </c>
@@ -2076,10 +2075,10 @@
         <v>80</v>
       </c>
       <c r="C4" s="5">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="D4" s="5">
-        <v>1610</v>
+        <v>1650</v>
       </c>
       <c r="E4" s="5">
         <v>2797</v>
@@ -2088,7 +2087,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>302012</v>
       </c>
@@ -2096,10 +2095,10 @@
         <v>79</v>
       </c>
       <c r="C5" s="5">
-        <v>2500</v>
+        <v>2540</v>
       </c>
       <c r="D5" s="5">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="E5" s="5">
         <v>2975</v>
@@ -2108,7 +2107,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>302015</v>
       </c>
@@ -2116,10 +2115,10 @@
         <v>92</v>
       </c>
       <c r="C6" s="5">
-        <v>2240</v>
+        <v>2270</v>
       </c>
       <c r="D6" s="5">
-        <v>1540</v>
+        <v>1560</v>
       </c>
       <c r="E6" s="5">
         <v>2666</v>
@@ -2128,7 +2127,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>302068</v>
       </c>
@@ -2136,10 +2135,10 @@
         <v>121</v>
       </c>
       <c r="C7" s="5">
-        <v>3250</v>
+        <v>3310</v>
       </c>
       <c r="D7" s="5">
-        <v>2230</v>
+        <v>2270</v>
       </c>
       <c r="E7" s="5">
         <v>3868</v>
@@ -2148,7 +2147,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>302067</v>
       </c>
@@ -2156,10 +2155,10 @@
         <v>122</v>
       </c>
       <c r="C8" s="5">
-        <v>2190</v>
+        <v>2220</v>
       </c>
       <c r="D8" s="5">
-        <v>1500</v>
+        <v>1520</v>
       </c>
       <c r="E8" s="5">
         <v>2606</v>
@@ -2168,7 +2167,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>302023</v>
       </c>
@@ -2176,10 +2175,10 @@
         <v>135</v>
       </c>
       <c r="C9" s="5">
-        <v>2160</v>
+        <v>2190</v>
       </c>
       <c r="D9" s="5">
-        <v>1480</v>
+        <v>1500</v>
       </c>
       <c r="E9" s="5">
         <v>2570</v>
@@ -2188,7 +2187,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>302048</v>
       </c>
@@ -2196,10 +2195,10 @@
         <v>217</v>
       </c>
       <c r="C10" s="5">
-        <v>9380</v>
+        <v>9540</v>
       </c>
       <c r="D10" s="5">
-        <v>6450</v>
+        <v>6560</v>
       </c>
       <c r="E10" s="5">
         <v>11162</v>
@@ -2208,7 +2207,7 @@
         <v>8372</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>302040</v>
       </c>
@@ -2216,10 +2215,10 @@
         <v>204</v>
       </c>
       <c r="C11" s="5">
-        <v>2060</v>
+        <v>2100</v>
       </c>
       <c r="D11" s="5">
-        <v>1410</v>
+        <v>1440</v>
       </c>
       <c r="E11" s="5">
         <v>2451</v>
@@ -2228,7 +2227,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>302042</v>
       </c>
@@ -2236,10 +2235,10 @@
         <v>207</v>
       </c>
       <c r="C12" s="5">
-        <v>2960</v>
+        <v>3010</v>
       </c>
       <c r="D12" s="5">
-        <v>2030</v>
+        <v>2070</v>
       </c>
       <c r="E12" s="5">
         <v>3522</v>
@@ -2248,7 +2247,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>302045</v>
       </c>
@@ -2256,10 +2255,10 @@
         <v>209</v>
       </c>
       <c r="C13" s="5">
-        <v>3620</v>
+        <v>3680</v>
       </c>
       <c r="D13" s="5">
-        <v>2490</v>
+        <v>2530</v>
       </c>
       <c r="E13" s="5">
         <v>4308</v>
@@ -2268,7 +2267,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>302047</v>
       </c>
@@ -2276,10 +2275,10 @@
         <v>216</v>
       </c>
       <c r="C14" s="5">
-        <v>2020</v>
+        <v>2050</v>
       </c>
       <c r="D14" s="5">
-        <v>1390</v>
+        <v>1410</v>
       </c>
       <c r="E14" s="5">
         <v>2404</v>
@@ -2288,7 +2287,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>301041</v>
       </c>
@@ -2296,10 +2295,10 @@
         <v>228</v>
       </c>
       <c r="C15" s="5">
-        <v>7300</v>
+        <v>7420</v>
       </c>
       <c r="D15" s="5">
-        <v>5020</v>
+        <v>5100</v>
       </c>
       <c r="E15" s="5">
         <v>8687</v>
@@ -2308,7 +2307,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>241</v>
       </c>
@@ -2328,7 +2327,7 @@
         <v>8474</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>302030</v>
       </c>
@@ -2336,10 +2335,10 @@
         <v>153</v>
       </c>
       <c r="C17" s="5">
-        <v>3860</v>
+        <v>3920</v>
       </c>
       <c r="D17" s="5">
-        <v>2650</v>
+        <v>2690</v>
       </c>
       <c r="E17" s="5">
         <v>4593</v>
@@ -2348,7 +2347,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>302057</v>
       </c>
@@ -2356,10 +2355,10 @@
         <v>299</v>
       </c>
       <c r="C18" s="5">
-        <v>2130</v>
+        <v>2160</v>
       </c>
       <c r="D18" s="5">
-        <v>1460</v>
+        <v>1480</v>
       </c>
       <c r="E18" s="5">
         <v>2535</v>
@@ -2368,7 +2367,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>302075</v>
       </c>
@@ -2376,10 +2375,10 @@
         <v>380</v>
       </c>
       <c r="C19" s="5">
-        <v>14080</v>
+        <v>14340</v>
       </c>
       <c r="D19" s="5">
-        <v>9680</v>
+        <v>9860</v>
       </c>
       <c r="E19" s="5">
         <v>16755</v>
@@ -2388,7 +2387,7 @@
         <v>12566</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>302076</v>
       </c>
@@ -2396,10 +2395,10 @@
         <v>381</v>
       </c>
       <c r="C20" s="5">
-        <v>16500</v>
+        <v>16780</v>
       </c>
       <c r="D20" s="5">
-        <v>11340</v>
+        <v>11530</v>
       </c>
       <c r="E20" s="5">
         <v>19635</v>
@@ -2408,7 +2407,7 @@
         <v>14726</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>302034</v>
       </c>
@@ -2416,10 +2415,10 @@
         <v>382</v>
       </c>
       <c r="C21" s="5">
-        <v>10030</v>
+        <v>10210</v>
       </c>
       <c r="D21" s="5">
-        <v>6890</v>
+        <v>7020</v>
       </c>
       <c r="E21" s="5">
         <v>11936</v>
@@ -2428,7 +2427,7 @@
         <v>8952</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>305031</v>
       </c>
@@ -2436,10 +2435,10 @@
         <v>400</v>
       </c>
       <c r="C22" s="5">
-        <v>9810</v>
+        <v>9980</v>
       </c>
       <c r="D22" s="5">
-        <v>6740</v>
+        <v>6860</v>
       </c>
       <c r="E22" s="5">
         <v>11674</v>
@@ -2448,7 +2447,7 @@
         <v>8756</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>405</v>
       </c>
@@ -2468,7 +2467,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>302100</v>
       </c>
@@ -2476,10 +2475,10 @@
         <v>407</v>
       </c>
       <c r="C24" s="5">
-        <v>2370</v>
+        <v>2420</v>
       </c>
       <c r="D24" s="5">
-        <v>1630</v>
+        <v>1660</v>
       </c>
       <c r="E24" s="5">
         <v>2820</v>
@@ -2488,7 +2487,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>302063</v>
       </c>
@@ -2496,10 +2495,10 @@
         <v>454</v>
       </c>
       <c r="C25" s="5">
-        <v>2990</v>
+        <v>3040</v>
       </c>
       <c r="D25" s="5">
-        <v>2050</v>
+        <v>2090</v>
       </c>
       <c r="E25" s="5">
         <v>3558</v>
@@ -2508,7 +2507,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>302064</v>
       </c>
@@ -2516,10 +2515,10 @@
         <v>461</v>
       </c>
       <c r="C26" s="5">
-        <v>2850</v>
+        <v>2900</v>
       </c>
       <c r="D26" s="5">
-        <v>1960</v>
+        <v>1990</v>
       </c>
       <c r="E26" s="5">
         <v>3392</v>
@@ -2528,7 +2527,7 @@
         <v>2544</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>422</v>
       </c>
@@ -2548,7 +2547,7 @@
         <v>4577</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>302024</v>
       </c>
@@ -2556,10 +2555,10 @@
         <v>114</v>
       </c>
       <c r="C28" s="5">
-        <v>4750</v>
+        <v>4830</v>
       </c>
       <c r="D28" s="5">
-        <v>3260</v>
+        <v>3320</v>
       </c>
       <c r="E28" s="5">
         <v>5653</v>
@@ -2568,7 +2567,7 @@
         <v>4240</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>309010</v>
       </c>
@@ -2576,10 +2575,10 @@
         <v>134</v>
       </c>
       <c r="C29" s="5">
-        <v>2500</v>
+        <v>2540</v>
       </c>
       <c r="D29" s="5">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="E29" s="5">
         <v>2975</v>
@@ -2588,7 +2587,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>309013</v>
       </c>
@@ -2596,10 +2595,10 @@
         <v>284</v>
       </c>
       <c r="C30" s="5">
-        <v>4580</v>
+        <v>4660</v>
       </c>
       <c r="D30" s="5">
-        <v>3150</v>
+        <v>3200</v>
       </c>
       <c r="E30" s="5">
         <v>5450</v>
@@ -2608,7 +2607,7 @@
         <v>4088</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>305070</v>
       </c>
@@ -2616,10 +2615,10 @@
         <v>58</v>
       </c>
       <c r="C31" s="5">
-        <v>14690</v>
+        <v>14940</v>
       </c>
       <c r="D31" s="5">
-        <v>10100</v>
+        <v>10270</v>
       </c>
       <c r="E31" s="5">
         <v>17481</v>
@@ -2628,7 +2627,7 @@
         <v>13111</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>303031</v>
       </c>
@@ -2636,10 +2635,10 @@
         <v>255</v>
       </c>
       <c r="C32" s="5">
-        <v>22260</v>
+        <v>22660</v>
       </c>
       <c r="D32" s="5">
-        <v>15300</v>
+        <v>15580</v>
       </c>
       <c r="E32" s="5">
         <v>26489</v>
@@ -2648,7 +2647,7 @@
         <v>19867</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>303030</v>
       </c>
@@ -2656,10 +2655,10 @@
         <v>179</v>
       </c>
       <c r="C33" s="5">
-        <v>8700</v>
+        <v>8860</v>
       </c>
       <c r="D33" s="5">
-        <v>5980</v>
+        <v>6090</v>
       </c>
       <c r="E33" s="5">
         <v>10353</v>
@@ -2668,7 +2667,7 @@
         <v>7765</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>303015</v>
       </c>
@@ -2676,10 +2675,10 @@
         <v>243</v>
       </c>
       <c r="C34" s="5">
-        <v>8860</v>
+        <v>9020</v>
       </c>
       <c r="D34" s="5">
-        <v>6090</v>
+        <v>6200</v>
       </c>
       <c r="E34" s="5">
         <v>10543</v>
@@ -2688,7 +2687,7 @@
         <v>7907</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>303024</v>
       </c>
@@ -2696,10 +2695,10 @@
         <v>448</v>
       </c>
       <c r="C35" s="5">
-        <v>7300</v>
+        <v>7420</v>
       </c>
       <c r="D35" s="5">
-        <v>5020</v>
+        <v>5100</v>
       </c>
       <c r="E35" s="5">
         <v>8687</v>
@@ -2708,7 +2707,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>303017</v>
       </c>
@@ -2716,10 +2715,10 @@
         <v>254</v>
       </c>
       <c r="C36" s="5">
-        <v>8260</v>
+        <v>8400</v>
       </c>
       <c r="D36" s="5">
-        <v>5680</v>
+        <v>5770</v>
       </c>
       <c r="E36" s="5">
         <v>9829</v>
@@ -2728,7 +2727,7 @@
         <v>7372</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>303026</v>
       </c>
@@ -2736,10 +2735,10 @@
         <v>450</v>
       </c>
       <c r="C37" s="5">
-        <v>8400</v>
+        <v>8540</v>
       </c>
       <c r="D37" s="5">
-        <v>5770</v>
+        <v>5870</v>
       </c>
       <c r="E37" s="5">
         <v>9996</v>
@@ -2748,7 +2747,7 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>303027</v>
       </c>
@@ -2756,10 +2755,10 @@
         <v>451</v>
       </c>
       <c r="C38" s="5">
-        <v>7300</v>
+        <v>7420</v>
       </c>
       <c r="D38" s="5">
-        <v>5020</v>
+        <v>5100</v>
       </c>
       <c r="E38" s="5">
         <v>8687</v>
@@ -2768,7 +2767,7 @@
         <v>6515</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>303028</v>
       </c>
@@ -2776,10 +2775,10 @@
         <v>463</v>
       </c>
       <c r="C39" s="5">
-        <v>7580</v>
+        <v>7710</v>
       </c>
       <c r="D39" s="5">
-        <v>5210</v>
+        <v>5300</v>
       </c>
       <c r="E39" s="5">
         <v>9020</v>
@@ -2788,7 +2787,7 @@
         <v>6765</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>306169</v>
       </c>
@@ -2796,10 +2795,10 @@
         <v>52</v>
       </c>
       <c r="C40" s="5">
-        <v>8720</v>
+        <v>8880</v>
       </c>
       <c r="D40" s="5">
-        <v>5990</v>
+        <v>6100</v>
       </c>
       <c r="E40" s="5">
         <v>10377</v>
@@ -2808,7 +2807,7 @@
         <v>7783</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>302077</v>
       </c>
@@ -2816,10 +2815,10 @@
         <v>494</v>
       </c>
       <c r="C41" s="5">
-        <v>12220</v>
+        <v>12450</v>
       </c>
       <c r="D41" s="5">
-        <v>8400</v>
+        <v>8560</v>
       </c>
       <c r="E41" s="5">
         <v>14542</v>
@@ -2828,7 +2827,7 @@
         <v>10907</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>302078</v>
       </c>
@@ -2836,10 +2835,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="5">
-        <v>27170</v>
+        <v>27650</v>
       </c>
       <c r="D42" s="5">
-        <v>18680</v>
+        <v>19010</v>
       </c>
       <c r="E42" s="5">
         <v>32332</v>
@@ -2848,7 +2847,7 @@
         <v>24249</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>309022</v>
       </c>
@@ -2856,10 +2855,10 @@
         <v>303</v>
       </c>
       <c r="C43" s="5">
-        <v>3090</v>
+        <v>3140</v>
       </c>
       <c r="D43" s="5">
-        <v>2120</v>
+        <v>2160</v>
       </c>
       <c r="E43" s="5">
         <v>3677</v>
@@ -2868,7 +2867,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>306034</v>
       </c>
@@ -2876,10 +2875,10 @@
         <v>112</v>
       </c>
       <c r="C44" s="5">
-        <v>8750</v>
+        <v>8910</v>
       </c>
       <c r="D44" s="5">
-        <v>6010</v>
+        <v>6120</v>
       </c>
       <c r="E44" s="5">
         <v>10413</v>
@@ -2888,7 +2887,7 @@
         <v>7810</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>306007</v>
       </c>
@@ -2896,10 +2895,10 @@
         <v>125</v>
       </c>
       <c r="C45" s="5">
-        <v>6700</v>
+        <v>6820</v>
       </c>
       <c r="D45" s="5">
-        <v>4600</v>
+        <v>4690</v>
       </c>
       <c r="E45" s="5">
         <v>7973</v>
@@ -2908,7 +2907,7 @@
         <v>5980</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>306008</v>
       </c>
@@ -2916,10 +2915,10 @@
         <v>147</v>
       </c>
       <c r="C46" s="5">
-        <v>5860</v>
+        <v>5950</v>
       </c>
       <c r="D46" s="5">
-        <v>4030</v>
+        <v>4090</v>
       </c>
       <c r="E46" s="5">
         <v>6973</v>
@@ -2928,7 +2927,7 @@
         <v>5230</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>306016</v>
       </c>
@@ -2936,10 +2935,10 @@
         <v>295</v>
       </c>
       <c r="C47" s="5">
-        <v>4780</v>
+        <v>4860</v>
       </c>
       <c r="D47" s="5">
-        <v>3280</v>
+        <v>3340</v>
       </c>
       <c r="E47" s="5">
         <v>5688</v>
@@ -2948,7 +2947,7 @@
         <v>4266</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>308044</v>
       </c>
@@ -2956,10 +2955,10 @@
         <v>202</v>
       </c>
       <c r="C48" s="5">
-        <v>12560</v>
+        <v>12780</v>
       </c>
       <c r="D48" s="5">
-        <v>8630</v>
+        <v>8780</v>
       </c>
       <c r="E48" s="5">
         <v>14946</v>
@@ -2968,7 +2967,7 @@
         <v>11210</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>308004</v>
       </c>
@@ -2976,10 +2975,10 @@
         <v>230</v>
       </c>
       <c r="C49" s="5">
-        <v>1900</v>
+        <v>1940</v>
       </c>
       <c r="D49" s="5">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="E49" s="5">
         <v>2261</v>
@@ -2988,7 +2987,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>308063</v>
       </c>
@@ -2996,10 +2995,10 @@
         <v>437</v>
       </c>
       <c r="C50" s="5">
-        <v>29560</v>
+        <v>30080</v>
       </c>
       <c r="D50" s="5">
-        <v>14780</v>
+        <v>15040</v>
       </c>
       <c r="E50" s="5">
         <v>39573</v>
@@ -3008,7 +3007,7 @@
         <v>29680</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>309024</v>
       </c>
@@ -3016,10 +3015,10 @@
         <v>425</v>
       </c>
       <c r="C51" s="5">
-        <v>1780</v>
+        <v>1810</v>
       </c>
       <c r="D51" s="5">
-        <v>1220</v>
+        <v>1240</v>
       </c>
       <c r="E51" s="5">
         <v>2118</v>
@@ -3028,7 +3027,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>306099</v>
       </c>
@@ -3036,10 +3035,10 @@
         <v>429</v>
       </c>
       <c r="C52" s="5">
-        <v>15540</v>
+        <v>15820</v>
       </c>
       <c r="D52" s="5">
-        <v>7770</v>
+        <v>7910</v>
       </c>
       <c r="E52" s="5">
         <v>20804</v>
@@ -3048,7 +3047,7 @@
         <v>15603</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>306005</v>
       </c>
@@ -3056,10 +3055,10 @@
         <v>447</v>
       </c>
       <c r="C53" s="5">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="D53" s="5">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="E53" s="5">
         <v>1333</v>
@@ -3068,7 +3067,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>306011</v>
       </c>
@@ -3076,10 +3075,10 @@
         <v>473</v>
       </c>
       <c r="C54" s="5">
-        <v>5970</v>
+        <v>6080</v>
       </c>
       <c r="D54" s="5">
-        <v>4100</v>
+        <v>4180</v>
       </c>
       <c r="E54" s="5">
         <v>7104</v>
@@ -3088,7 +3087,7 @@
         <v>5328</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>306023</v>
       </c>
@@ -3096,10 +3095,10 @@
         <v>148</v>
       </c>
       <c r="C55" s="5">
-        <v>10180</v>
+        <v>10350</v>
       </c>
       <c r="D55" s="5">
-        <v>7000</v>
+        <v>7110</v>
       </c>
       <c r="E55" s="5">
         <v>12114</v>
@@ -3108,7 +3107,7 @@
         <v>9086</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>306038</v>
       </c>
@@ -3116,10 +3115,10 @@
         <v>410</v>
       </c>
       <c r="C56" s="5">
-        <v>4350</v>
+        <v>4430</v>
       </c>
       <c r="D56" s="5">
-        <v>2990</v>
+        <v>3040</v>
       </c>
       <c r="E56" s="5">
         <v>5177</v>
@@ -3128,7 +3127,7 @@
         <v>3883</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>306079</v>
       </c>
@@ -3136,10 +3135,10 @@
         <v>486</v>
       </c>
       <c r="C57" s="5">
-        <v>8830</v>
+        <v>8990</v>
       </c>
       <c r="D57" s="5">
-        <v>6070</v>
+        <v>6180</v>
       </c>
       <c r="E57" s="5">
         <v>10508</v>
@@ -3148,7 +3147,7 @@
         <v>7881</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>306081</v>
       </c>
@@ -3156,10 +3155,10 @@
         <v>488</v>
       </c>
       <c r="C58" s="5">
-        <v>13490</v>
+        <v>13730</v>
       </c>
       <c r="D58" s="5">
-        <v>9270</v>
+        <v>9440</v>
       </c>
       <c r="E58" s="5">
         <v>16053</v>
@@ -3168,7 +3167,7 @@
         <v>12040</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>306056</v>
       </c>
@@ -3176,10 +3175,10 @@
         <v>411</v>
       </c>
       <c r="C59" s="5">
-        <v>6420</v>
+        <v>6530</v>
       </c>
       <c r="D59" s="5">
-        <v>4410</v>
+        <v>4490</v>
       </c>
       <c r="E59" s="5">
         <v>7640</v>
@@ -3188,7 +3187,7 @@
         <v>5730</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>308005</v>
       </c>
@@ -3196,10 +3195,10 @@
         <v>263</v>
       </c>
       <c r="C60" s="5">
-        <v>1900</v>
+        <v>1940</v>
       </c>
       <c r="D60" s="5">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="E60" s="5">
         <v>2261</v>
@@ -3208,7 +3207,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>306051</v>
       </c>
@@ -3216,10 +3215,10 @@
         <v>219</v>
       </c>
       <c r="C61" s="5">
-        <v>3390</v>
+        <v>3460</v>
       </c>
       <c r="D61" s="5">
-        <v>2330</v>
+        <v>2380</v>
       </c>
       <c r="E61" s="5">
         <v>4034</v>
@@ -3228,7 +3227,7 @@
         <v>3026</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>308013</v>
       </c>
@@ -3236,10 +3235,10 @@
         <v>172</v>
       </c>
       <c r="C62" s="5">
-        <v>1310</v>
+        <v>1330</v>
       </c>
       <c r="D62" s="5">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="E62" s="5">
         <v>1559</v>
@@ -3248,7 +3247,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>301036</v>
       </c>
@@ -3256,7 +3255,7 @@
         <v>224</v>
       </c>
       <c r="C63" s="5">
-        <v>1250</v>
+        <v>1260</v>
       </c>
       <c r="D63" s="5">
         <v>860</v>
@@ -3268,7 +3267,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>301038</v>
       </c>
@@ -3276,7 +3275,7 @@
         <v>227</v>
       </c>
       <c r="C64" s="5">
-        <v>1250</v>
+        <v>1260</v>
       </c>
       <c r="D64" s="5">
         <v>860</v>
@@ -3288,7 +3287,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>301045</v>
       </c>
@@ -3296,10 +3295,10 @@
         <v>229</v>
       </c>
       <c r="C65" s="5">
-        <v>4980</v>
+        <v>5070</v>
       </c>
       <c r="D65" s="5">
-        <v>3420</v>
+        <v>3480</v>
       </c>
       <c r="E65" s="5">
         <v>5926</v>
@@ -3308,7 +3307,7 @@
         <v>4445</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>301062</v>
       </c>
@@ -3316,10 +3315,10 @@
         <v>415</v>
       </c>
       <c r="C66" s="5">
-        <v>1700</v>
+        <v>1730</v>
       </c>
       <c r="D66" s="5">
-        <v>1170</v>
+        <v>1190</v>
       </c>
       <c r="E66" s="5">
         <v>2023</v>
@@ -3328,7 +3327,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>301063</v>
       </c>
@@ -3336,10 +3335,10 @@
         <v>416</v>
       </c>
       <c r="C67" s="5">
-        <v>1580</v>
+        <v>1620</v>
       </c>
       <c r="D67" s="5">
-        <v>1080</v>
+        <v>1110</v>
       </c>
       <c r="E67" s="5">
         <v>1880</v>
@@ -3348,7 +3347,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>301065</v>
       </c>
@@ -3356,10 +3355,10 @@
         <v>418</v>
       </c>
       <c r="C68" s="5">
-        <v>1180</v>
+        <v>1200</v>
       </c>
       <c r="D68" s="5">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="E68" s="5">
         <v>1404</v>
@@ -3368,7 +3367,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>301067</v>
       </c>
@@ -3376,10 +3375,10 @@
         <v>420</v>
       </c>
       <c r="C69" s="5">
-        <v>2100</v>
+        <v>2130</v>
       </c>
       <c r="D69" s="5">
-        <v>1440</v>
+        <v>1460</v>
       </c>
       <c r="E69" s="5">
         <v>2499</v>
@@ -3388,7 +3387,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>301064</v>
       </c>
@@ -3396,7 +3395,7 @@
         <v>417</v>
       </c>
       <c r="C70" s="5">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="D70" s="5">
         <v>840</v>
@@ -3408,7 +3407,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>301066</v>
       </c>
@@ -3416,10 +3415,10 @@
         <v>419</v>
       </c>
       <c r="C71" s="5">
-        <v>2050</v>
+        <v>2080</v>
       </c>
       <c r="D71" s="5">
-        <v>1410</v>
+        <v>1430</v>
       </c>
       <c r="E71" s="5">
         <v>2440</v>
@@ -3428,7 +3427,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>301068</v>
       </c>
@@ -3436,10 +3435,10 @@
         <v>421</v>
       </c>
       <c r="C72" s="5">
-        <v>1620</v>
+        <v>1650</v>
       </c>
       <c r="D72" s="5">
-        <v>1110</v>
+        <v>1130</v>
       </c>
       <c r="E72" s="5">
         <v>1928</v>
@@ -3448,7 +3447,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>301086</v>
       </c>
@@ -3456,7 +3455,7 @@
         <v>475</v>
       </c>
       <c r="C73" s="5">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="D73" s="5">
         <v>620</v>
@@ -3468,7 +3467,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>301059</v>
       </c>
@@ -3476,10 +3475,10 @@
         <v>444</v>
       </c>
       <c r="C74" s="5">
-        <v>2500</v>
+        <v>2540</v>
       </c>
       <c r="D74" s="5">
-        <v>1720</v>
+        <v>1740</v>
       </c>
       <c r="E74" s="5">
         <v>2975</v>
@@ -3488,7 +3487,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>301072</v>
       </c>
@@ -3496,10 +3495,10 @@
         <v>445</v>
       </c>
       <c r="C75" s="5">
-        <v>2420</v>
+        <v>2460</v>
       </c>
       <c r="D75" s="5">
-        <v>1660</v>
+        <v>1690</v>
       </c>
       <c r="E75" s="5">
         <v>2880</v>
@@ -3508,7 +3507,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>301085</v>
       </c>
@@ -3516,10 +3515,10 @@
         <v>465</v>
       </c>
       <c r="C76" s="5">
-        <v>3860</v>
+        <v>3920</v>
       </c>
       <c r="D76" s="5">
-        <v>2650</v>
+        <v>2690</v>
       </c>
       <c r="E76" s="5">
         <v>4593</v>
@@ -3528,7 +3527,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>4</v>
       </c>
@@ -3548,7 +3547,7 @@
         <v>62885</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>303029</v>
       </c>
@@ -3556,10 +3555,10 @@
         <v>6</v>
       </c>
       <c r="C78" s="5">
-        <v>11410</v>
+        <v>11620</v>
       </c>
       <c r="D78" s="5">
-        <v>7840</v>
+        <v>7990</v>
       </c>
       <c r="E78" s="5">
         <v>13578</v>
@@ -3568,7 +3567,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
@@ -3588,7 +3587,7 @@
         <v>43472</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>10</v>
       </c>
@@ -3608,7 +3607,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>305086</v>
       </c>
@@ -3616,10 +3615,10 @@
         <v>503</v>
       </c>
       <c r="C81" s="5">
-        <v>17070</v>
+        <v>17380</v>
       </c>
       <c r="D81" s="5">
-        <v>11730</v>
+        <v>11950</v>
       </c>
       <c r="E81" s="5">
         <v>20313</v>
@@ -3628,7 +3627,7 @@
         <v>15235</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>12</v>
       </c>
@@ -3648,7 +3647,7 @@
         <v>134581</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>301002</v>
       </c>
@@ -3656,10 +3655,10 @@
         <v>14</v>
       </c>
       <c r="C83" s="5">
-        <v>8080</v>
+        <v>8220</v>
       </c>
       <c r="D83" s="5">
-        <v>5550</v>
+        <v>5650</v>
       </c>
       <c r="E83" s="5">
         <v>9615</v>
@@ -3668,7 +3667,7 @@
         <v>7211</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>302035</v>
       </c>
@@ -3676,10 +3675,10 @@
         <v>195</v>
       </c>
       <c r="C84" s="5">
-        <v>10080</v>
+        <v>10260</v>
       </c>
       <c r="D84" s="5">
-        <v>6930</v>
+        <v>7050</v>
       </c>
       <c r="E84" s="5">
         <v>11995</v>
@@ -3688,7 +3687,7 @@
         <v>8996</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
@@ -3708,7 +3707,7 @@
         <v>15140</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>19</v>
       </c>
@@ -3728,7 +3727,7 @@
         <v>15140</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>302050</v>
       </c>
@@ -3736,10 +3735,10 @@
         <v>21</v>
       </c>
       <c r="C87" s="5">
-        <v>8580</v>
+        <v>8720</v>
       </c>
       <c r="D87" s="5">
-        <v>5900</v>
+        <v>5990</v>
       </c>
       <c r="E87" s="5">
         <v>10210</v>
@@ -3748,7 +3747,7 @@
         <v>7658</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>306069</v>
       </c>
@@ -3756,10 +3755,10 @@
         <v>504</v>
       </c>
       <c r="C88" s="5">
-        <v>10060</v>
+        <v>10240</v>
       </c>
       <c r="D88" s="5">
-        <v>6910</v>
+        <v>7040</v>
       </c>
       <c r="E88" s="5">
         <v>11971</v>
@@ -3768,7 +3767,7 @@
         <v>8978</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>24</v>
       </c>
@@ -3788,7 +3787,7 @@
         <v>9063</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>303002</v>
       </c>
@@ -3796,10 +3795,10 @@
         <v>23</v>
       </c>
       <c r="C90" s="5">
-        <v>11410</v>
+        <v>11620</v>
       </c>
       <c r="D90" s="5">
-        <v>7840</v>
+        <v>7990</v>
       </c>
       <c r="E90" s="5">
         <v>13578</v>
@@ -3808,7 +3807,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>305001</v>
       </c>
@@ -3816,10 +3815,10 @@
         <v>26</v>
       </c>
       <c r="C91" s="5">
-        <v>8660</v>
+        <v>8820</v>
       </c>
       <c r="D91" s="5">
-        <v>5950</v>
+        <v>6060</v>
       </c>
       <c r="E91" s="5">
         <v>10305</v>
@@ -3828,7 +3827,7 @@
         <v>7729</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>305003</v>
       </c>
@@ -3836,10 +3835,10 @@
         <v>27</v>
       </c>
       <c r="C92" s="5">
-        <v>8400</v>
+        <v>8540</v>
       </c>
       <c r="D92" s="5">
-        <v>5770</v>
+        <v>5870</v>
       </c>
       <c r="E92" s="5">
         <v>9996</v>
@@ -3848,7 +3847,7 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>28</v>
       </c>
@@ -3868,7 +3867,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>309006</v>
       </c>
@@ -3876,10 +3875,10 @@
         <v>30</v>
       </c>
       <c r="C94" s="5">
-        <v>4370</v>
+        <v>4450</v>
       </c>
       <c r="D94" s="5">
-        <v>3000</v>
+        <v>3060</v>
       </c>
       <c r="E94" s="5">
         <v>5200</v>
@@ -3888,7 +3887,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>302008</v>
       </c>
@@ -3896,10 +3895,10 @@
         <v>31</v>
       </c>
       <c r="C95" s="5">
-        <v>3860</v>
+        <v>3920</v>
       </c>
       <c r="D95" s="5">
-        <v>2650</v>
+        <v>2690</v>
       </c>
       <c r="E95" s="5">
         <v>4593</v>
@@ -3908,7 +3907,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>32</v>
       </c>
@@ -3928,7 +3927,7 @@
         <v>66263</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>35</v>
       </c>
@@ -3948,7 +3947,7 @@
         <v>66263</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>38</v>
       </c>
@@ -3968,7 +3967,7 @@
         <v>79651</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>303003</v>
       </c>
@@ -3976,10 +3975,10 @@
         <v>39</v>
       </c>
       <c r="C99" s="5">
-        <v>9010</v>
+        <v>9170</v>
       </c>
       <c r="D99" s="5">
-        <v>6190</v>
+        <v>6300</v>
       </c>
       <c r="E99" s="5">
         <v>10722</v>
@@ -3988,7 +3987,7 @@
         <v>8042</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>305105</v>
       </c>
@@ -3996,10 +3995,10 @@
         <v>506</v>
       </c>
       <c r="C100" s="5">
-        <v>40400</v>
+        <v>41120</v>
       </c>
       <c r="D100" s="5">
-        <v>20200</v>
+        <v>20560</v>
       </c>
       <c r="E100" s="5">
         <v>54086</v>
@@ -4008,7 +4007,7 @@
         <v>40565</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>305007</v>
       </c>
@@ -4016,10 +4015,10 @@
         <v>51</v>
       </c>
       <c r="C101" s="5">
-        <v>9760</v>
+        <v>9940</v>
       </c>
       <c r="D101" s="5">
-        <v>6710</v>
+        <v>6830</v>
       </c>
       <c r="E101" s="5">
         <v>11614</v>
@@ -4028,7 +4027,7 @@
         <v>8711</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>305005</v>
       </c>
@@ -4036,10 +4035,10 @@
         <v>47</v>
       </c>
       <c r="C102" s="5">
-        <v>12220</v>
+        <v>12450</v>
       </c>
       <c r="D102" s="5">
-        <v>8400</v>
+        <v>8560</v>
       </c>
       <c r="E102" s="5">
         <v>14542</v>
@@ -4048,7 +4047,7 @@
         <v>10907</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>305082</v>
       </c>
@@ -4056,10 +4055,10 @@
         <v>45</v>
       </c>
       <c r="C103" s="5">
-        <v>26180</v>
+        <v>26640</v>
       </c>
       <c r="D103" s="5">
-        <v>18000</v>
+        <v>18310</v>
       </c>
       <c r="E103" s="5">
         <v>31154</v>
@@ -4068,7 +4067,7 @@
         <v>23366</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>305081</v>
       </c>
@@ -4076,10 +4075,10 @@
         <v>42</v>
       </c>
       <c r="C104" s="5">
-        <v>18300</v>
+        <v>18620</v>
       </c>
       <c r="D104" s="5">
-        <v>12580</v>
+        <v>12800</v>
       </c>
       <c r="E104" s="5">
         <v>21777</v>
@@ -4088,7 +4087,7 @@
         <v>16333</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>305108</v>
       </c>
@@ -4096,10 +4095,10 @@
         <v>43</v>
       </c>
       <c r="C105" s="5">
-        <v>22820</v>
+        <v>23220</v>
       </c>
       <c r="D105" s="5">
-        <v>11410</v>
+        <v>11610</v>
       </c>
       <c r="E105" s="5">
         <v>30550</v>
@@ -4108,7 +4107,7 @@
         <v>22913</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>305085</v>
       </c>
@@ -4116,10 +4115,10 @@
         <v>44</v>
       </c>
       <c r="C106" s="5">
-        <v>37170</v>
+        <v>37820</v>
       </c>
       <c r="D106" s="5">
-        <v>25550</v>
+        <v>26000</v>
       </c>
       <c r="E106" s="5">
         <v>44232</v>
@@ -4128,7 +4127,7 @@
         <v>33174</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>305124</v>
       </c>
@@ -4136,10 +4135,10 @@
         <v>414</v>
       </c>
       <c r="C107" s="5">
-        <v>34680</v>
+        <v>35290</v>
       </c>
       <c r="D107" s="5">
-        <v>17340</v>
+        <v>17640</v>
       </c>
       <c r="E107" s="5">
         <v>49523</v>
@@ -4148,7 +4147,7 @@
         <v>37142</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>306041</v>
       </c>
@@ -4156,10 +4155,10 @@
         <v>456</v>
       </c>
       <c r="C108" s="5">
-        <v>8030</v>
+        <v>8180</v>
       </c>
       <c r="D108" s="5">
-        <v>5520</v>
+        <v>5620</v>
       </c>
       <c r="E108" s="5">
         <v>9556</v>
@@ -4168,7 +4167,7 @@
         <v>7167</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>305004</v>
       </c>
@@ -4176,10 +4175,10 @@
         <v>436</v>
       </c>
       <c r="C109" s="5">
-        <v>17380</v>
+        <v>17680</v>
       </c>
       <c r="D109" s="5">
-        <v>11950</v>
+        <v>12150</v>
       </c>
       <c r="E109" s="5">
         <v>20682</v>
@@ -4188,7 +4187,7 @@
         <v>15512</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>48</v>
       </c>
@@ -4208,7 +4207,7 @@
         <v>75290</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>49</v>
       </c>
@@ -4228,7 +4227,7 @@
         <v>75290</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>305008</v>
       </c>
@@ -4236,10 +4235,10 @@
         <v>53</v>
       </c>
       <c r="C112" s="5">
-        <v>7550</v>
+        <v>7680</v>
       </c>
       <c r="D112" s="5">
-        <v>5190</v>
+        <v>5280</v>
       </c>
       <c r="E112" s="5">
         <v>8985</v>
@@ -4248,7 +4247,7 @@
         <v>6739</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>305009</v>
       </c>
@@ -4256,10 +4255,10 @@
         <v>55</v>
       </c>
       <c r="C113" s="5">
-        <v>11410</v>
+        <v>11620</v>
       </c>
       <c r="D113" s="5">
-        <v>7840</v>
+        <v>7990</v>
       </c>
       <c r="E113" s="5">
         <v>13578</v>
@@ -4268,7 +4267,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>56</v>
       </c>
@@ -4288,7 +4287,7 @@
         <v>185578</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>59</v>
       </c>
@@ -4308,7 +4307,7 @@
         <v>241367</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>63</v>
       </c>
@@ -4328,7 +4327,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>301008</v>
       </c>
@@ -4336,10 +4335,10 @@
         <v>65</v>
       </c>
       <c r="C117" s="5">
-        <v>8450</v>
+        <v>8590</v>
       </c>
       <c r="D117" s="5">
-        <v>5810</v>
+        <v>5900</v>
       </c>
       <c r="E117" s="5">
         <v>10056</v>
@@ -4348,7 +4347,7 @@
         <v>7542</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>302070</v>
       </c>
@@ -4356,10 +4355,10 @@
         <v>66</v>
       </c>
       <c r="C118" s="5">
-        <v>11170</v>
+        <v>11360</v>
       </c>
       <c r="D118" s="5">
-        <v>7680</v>
+        <v>7810</v>
       </c>
       <c r="E118" s="5">
         <v>13292</v>
@@ -4368,7 +4367,7 @@
         <v>9969</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>68</v>
       </c>
@@ -4388,7 +4387,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>309034</v>
       </c>
@@ -4396,10 +4395,10 @@
         <v>67</v>
       </c>
       <c r="C120" s="5">
-        <v>47520</v>
+        <v>48360</v>
       </c>
       <c r="D120" s="5">
-        <v>23760</v>
+        <v>24180</v>
       </c>
       <c r="E120" s="5">
         <v>67859</v>
@@ -4408,7 +4407,7 @@
         <v>50894</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>71</v>
       </c>
@@ -4428,7 +4427,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>202232</v>
       </c>
@@ -4448,7 +4447,7 @@
         <v>42846</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>202233</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>42846</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>74</v>
       </c>
@@ -4488,7 +4487,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>76</v>
       </c>
@@ -4508,7 +4507,7 @@
         <v>26473</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>305010</v>
       </c>
@@ -4516,10 +4515,10 @@
         <v>78</v>
       </c>
       <c r="C126" s="5">
-        <v>12980</v>
+        <v>13200</v>
       </c>
       <c r="D126" s="5">
-        <v>8920</v>
+        <v>9070</v>
       </c>
       <c r="E126" s="5">
         <v>15446</v>
@@ -4528,7 +4527,7 @@
         <v>11585</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>306118</v>
       </c>
@@ -4536,10 +4535,10 @@
         <v>37</v>
       </c>
       <c r="C127" s="5">
-        <v>64090</v>
+        <v>65220</v>
       </c>
       <c r="D127" s="5">
-        <v>32040</v>
+        <v>32610</v>
       </c>
       <c r="E127" s="5">
         <v>91521</v>
@@ -4548,7 +4547,7 @@
         <v>68641</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>306013</v>
       </c>
@@ -4556,10 +4555,10 @@
         <v>509</v>
       </c>
       <c r="C128" s="5">
-        <v>11330</v>
+        <v>11540</v>
       </c>
       <c r="D128" s="5">
-        <v>7790</v>
+        <v>7930</v>
       </c>
       <c r="E128" s="5">
         <v>13483</v>
@@ -4568,7 +4567,7 @@
         <v>10112</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>81</v>
       </c>
@@ -4588,7 +4587,7 @@
         <v>15659</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>82</v>
       </c>
@@ -4608,7 +4607,7 @@
         <v>15659</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>306033</v>
       </c>
@@ -4616,10 +4615,10 @@
         <v>84</v>
       </c>
       <c r="C131" s="5">
-        <v>3340</v>
+        <v>3410</v>
       </c>
       <c r="D131" s="5">
-        <v>2290</v>
+        <v>2340</v>
       </c>
       <c r="E131" s="5">
         <v>3975</v>
@@ -4628,7 +4627,7 @@
         <v>2981</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>305170</v>
       </c>
@@ -4636,10 +4635,10 @@
         <v>54</v>
       </c>
       <c r="C132" s="5">
-        <v>15220</v>
+        <v>15490</v>
       </c>
       <c r="D132" s="5">
-        <v>10460</v>
+        <v>10650</v>
       </c>
       <c r="E132" s="5">
         <v>18112</v>
@@ -4648,7 +4647,7 @@
         <v>13584</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>85</v>
       </c>
@@ -4668,7 +4667,7 @@
         <v>154672</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>87</v>
       </c>
@@ -4688,7 +4687,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>89</v>
       </c>
@@ -4708,7 +4707,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>309008</v>
       </c>
@@ -4716,10 +4715,10 @@
         <v>91</v>
       </c>
       <c r="C136" s="5">
-        <v>3300</v>
+        <v>3360</v>
       </c>
       <c r="D136" s="5">
-        <v>2270</v>
+        <v>2310</v>
       </c>
       <c r="E136" s="5">
         <v>3927</v>
@@ -4728,7 +4727,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>308049</v>
       </c>
@@ -4736,10 +4735,10 @@
         <v>93</v>
       </c>
       <c r="C137" s="5">
-        <v>46190</v>
+        <v>47010</v>
       </c>
       <c r="D137" s="5">
-        <v>23090</v>
+        <v>23500</v>
       </c>
       <c r="E137" s="5">
         <v>61837</v>
@@ -4748,7 +4747,7 @@
         <v>46378</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>94</v>
       </c>
@@ -4768,7 +4767,7 @@
         <v>73377</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>96</v>
       </c>
@@ -4788,7 +4787,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>301029</v>
       </c>
@@ -4796,10 +4795,10 @@
         <v>201</v>
       </c>
       <c r="C140" s="5">
-        <v>7460</v>
+        <v>7580</v>
       </c>
       <c r="D140" s="5">
-        <v>5130</v>
+        <v>5210</v>
       </c>
       <c r="E140" s="5">
         <v>8877</v>
@@ -4808,7 +4807,7 @@
         <v>6658</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>305084</v>
       </c>
@@ -4816,10 +4815,10 @@
         <v>511</v>
       </c>
       <c r="C141" s="5">
-        <v>20800</v>
+        <v>21170</v>
       </c>
       <c r="D141" s="5">
-        <v>14300</v>
+        <v>14550</v>
       </c>
       <c r="E141" s="5">
         <v>24752</v>
@@ -4828,7 +4827,7 @@
         <v>18564</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>306084</v>
       </c>
@@ -4836,10 +4835,10 @@
         <v>231</v>
       </c>
       <c r="C142" s="5">
-        <v>114200</v>
+        <v>116220</v>
       </c>
       <c r="D142" s="5">
-        <v>57100</v>
+        <v>58110</v>
       </c>
       <c r="E142" s="5">
         <v>163078</v>
@@ -4848,7 +4847,7 @@
         <v>122309</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>306085</v>
       </c>
@@ -4856,10 +4855,10 @@
         <v>234</v>
       </c>
       <c r="C143" s="5">
-        <v>127070</v>
+        <v>129320</v>
       </c>
       <c r="D143" s="5">
-        <v>63530</v>
+        <v>64660</v>
       </c>
       <c r="E143" s="5">
         <v>181456</v>
@@ -4868,7 +4867,7 @@
         <v>136092</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>302017</v>
       </c>
@@ -4876,10 +4875,10 @@
         <v>98</v>
       </c>
       <c r="C144" s="5">
-        <v>3570</v>
+        <v>3630</v>
       </c>
       <c r="D144" s="5">
-        <v>2450</v>
+        <v>2490</v>
       </c>
       <c r="E144" s="5">
         <v>4248</v>
@@ -4888,7 +4887,7 @@
         <v>3186</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>303051</v>
       </c>
@@ -4896,10 +4895,10 @@
         <v>99</v>
       </c>
       <c r="C145" s="5">
-        <v>58750</v>
+        <v>59790</v>
       </c>
       <c r="D145" s="5">
-        <v>40390</v>
+        <v>41100</v>
       </c>
       <c r="E145" s="5">
         <v>69913</v>
@@ -4908,7 +4907,7 @@
         <v>52435</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>302019</v>
       </c>
@@ -4916,10 +4915,10 @@
         <v>100</v>
       </c>
       <c r="C146" s="5">
-        <v>5950</v>
+        <v>6060</v>
       </c>
       <c r="D146" s="5">
-        <v>4090</v>
+        <v>4160</v>
       </c>
       <c r="E146" s="5">
         <v>7081</v>
@@ -4928,7 +4927,7 @@
         <v>5311</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>101</v>
       </c>
@@ -4948,7 +4947,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>306061</v>
       </c>
@@ -4956,10 +4955,10 @@
         <v>512</v>
       </c>
       <c r="C148" s="5">
-        <v>9060</v>
+        <v>9220</v>
       </c>
       <c r="D148" s="5">
-        <v>6230</v>
+        <v>6340</v>
       </c>
       <c r="E148" s="5">
         <v>10781</v>
@@ -4968,7 +4967,7 @@
         <v>8086</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>103</v>
       </c>
@@ -4988,7 +4987,7 @@
         <v>74020</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>306097</v>
       </c>
@@ -4996,10 +4995,10 @@
         <v>105</v>
       </c>
       <c r="C150" s="5">
-        <v>42710</v>
+        <v>43470</v>
       </c>
       <c r="D150" s="5">
-        <v>21350</v>
+        <v>21730</v>
       </c>
       <c r="E150" s="5">
         <v>57178</v>
@@ -5008,7 +5007,7 @@
         <v>42884</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>106</v>
       </c>
@@ -5028,7 +5027,7 @@
         <v>29601</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>306182</v>
       </c>
@@ -5036,10 +5035,10 @@
         <v>413</v>
       </c>
       <c r="C152" s="5">
-        <v>29190</v>
+        <v>29710</v>
       </c>
       <c r="D152" s="5">
-        <v>14590</v>
+        <v>14850</v>
       </c>
       <c r="E152" s="5">
         <v>142633</v>
@@ -5048,7 +5047,7 @@
         <v>106975</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>109</v>
       </c>
@@ -5068,7 +5067,7 @@
         <v>129505</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>202242</v>
       </c>
@@ -5088,7 +5087,7 @@
         <v>23541</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>309012</v>
       </c>
@@ -5096,10 +5095,10 @@
         <v>165</v>
       </c>
       <c r="C155" s="5">
-        <v>2540</v>
+        <v>2590</v>
       </c>
       <c r="D155" s="5">
-        <v>1740</v>
+        <v>1780</v>
       </c>
       <c r="E155" s="5">
         <v>3023</v>
@@ -5108,7 +5107,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>302032</v>
       </c>
@@ -5116,10 +5115,10 @@
         <v>166</v>
       </c>
       <c r="C156" s="5">
-        <v>2080</v>
+        <v>2110</v>
       </c>
       <c r="D156" s="5">
-        <v>1430</v>
+        <v>1450</v>
       </c>
       <c r="E156" s="5">
         <v>2475</v>
@@ -5128,7 +5127,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>115</v>
       </c>
@@ -5148,7 +5147,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>117</v>
       </c>
@@ -5168,7 +5167,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>309036</v>
       </c>
@@ -5176,10 +5175,10 @@
         <v>119</v>
       </c>
       <c r="C159" s="5">
-        <v>32240</v>
+        <v>32810</v>
       </c>
       <c r="D159" s="5">
-        <v>16120</v>
+        <v>16400</v>
       </c>
       <c r="E159" s="5">
         <v>67231</v>
@@ -5188,7 +5187,7 @@
         <v>50423</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>302020</v>
       </c>
@@ -5196,10 +5195,10 @@
         <v>120</v>
       </c>
       <c r="C160" s="5">
-        <v>3310</v>
+        <v>3380</v>
       </c>
       <c r="D160" s="5">
-        <v>2270</v>
+        <v>2320</v>
       </c>
       <c r="E160" s="5">
         <v>3939</v>
@@ -5208,7 +5207,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>302021</v>
       </c>
@@ -5216,10 +5215,10 @@
         <v>123</v>
       </c>
       <c r="C161" s="5">
-        <v>4800</v>
+        <v>4880</v>
       </c>
       <c r="D161" s="5">
-        <v>3300</v>
+        <v>3350</v>
       </c>
       <c r="E161" s="5">
         <v>5712</v>
@@ -5228,7 +5227,7 @@
         <v>4284</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>305012</v>
       </c>
@@ -5236,10 +5235,10 @@
         <v>124</v>
       </c>
       <c r="C162" s="5">
-        <v>7550</v>
+        <v>7680</v>
       </c>
       <c r="D162" s="5">
-        <v>5190</v>
+        <v>5280</v>
       </c>
       <c r="E162" s="5">
         <v>8985</v>
@@ -5248,7 +5247,7 @@
         <v>6739</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>127</v>
       </c>
@@ -5268,7 +5267,7 @@
         <v>62885</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>303035</v>
       </c>
@@ -5276,10 +5275,10 @@
         <v>130</v>
       </c>
       <c r="C164" s="5">
-        <v>9140</v>
+        <v>9300</v>
       </c>
       <c r="D164" s="5">
-        <v>6280</v>
+        <v>6390</v>
       </c>
       <c r="E164" s="5">
         <v>10877</v>
@@ -5288,7 +5287,7 @@
         <v>8158</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>303056</v>
       </c>
@@ -5296,10 +5295,10 @@
         <v>131</v>
       </c>
       <c r="C165" s="5">
-        <v>49220</v>
+        <v>50090</v>
       </c>
       <c r="D165" s="5">
-        <v>24610</v>
+        <v>25040</v>
       </c>
       <c r="E165" s="5">
         <v>65893</v>
@@ -5308,7 +5307,7 @@
         <v>49420</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>303006</v>
       </c>
@@ -5316,10 +5315,10 @@
         <v>129</v>
       </c>
       <c r="C166" s="5">
-        <v>9010</v>
+        <v>9170</v>
       </c>
       <c r="D166" s="5">
-        <v>6190</v>
+        <v>6300</v>
       </c>
       <c r="E166" s="5">
         <v>10722</v>
@@ -5328,7 +5327,7 @@
         <v>8042</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>132</v>
       </c>
@@ -5348,7 +5347,7 @@
         <v>62885</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>302025</v>
       </c>
@@ -5356,10 +5355,10 @@
         <v>136</v>
       </c>
       <c r="C168" s="5">
-        <v>8560</v>
+        <v>8700</v>
       </c>
       <c r="D168" s="5">
-        <v>5880</v>
+        <v>5980</v>
       </c>
       <c r="E168" s="5">
         <v>10186</v>
@@ -5368,7 +5367,7 @@
         <v>7640</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>302026</v>
       </c>
@@ -5376,10 +5375,10 @@
         <v>137</v>
       </c>
       <c r="C169" s="5">
-        <v>6130</v>
+        <v>6240</v>
       </c>
       <c r="D169" s="5">
-        <v>4210</v>
+        <v>4290</v>
       </c>
       <c r="E169" s="5">
         <v>7295</v>
@@ -5388,7 +5387,7 @@
         <v>5471</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>139</v>
       </c>
@@ -5408,7 +5407,7 @@
         <v>115436</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>141</v>
       </c>
@@ -5428,7 +5427,7 @@
         <v>274739</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>143</v>
       </c>
@@ -5448,7 +5447,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>145</v>
       </c>
@@ -5468,7 +5467,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>303008</v>
       </c>
@@ -5476,10 +5475,10 @@
         <v>151</v>
       </c>
       <c r="C174" s="5">
-        <v>11250</v>
+        <v>11440</v>
       </c>
       <c r="D174" s="5">
-        <v>7730</v>
+        <v>7860</v>
       </c>
       <c r="E174" s="5">
         <v>13388</v>
@@ -5488,7 +5487,7 @@
         <v>10041</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>155</v>
       </c>
@@ -5508,7 +5507,7 @@
         <v>296153</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>801001</v>
       </c>
@@ -5516,10 +5515,10 @@
         <v>108</v>
       </c>
       <c r="C176" s="5">
-        <v>11180</v>
+        <v>11380</v>
       </c>
       <c r="D176" s="5">
-        <v>7680</v>
+        <v>7820</v>
       </c>
       <c r="E176" s="5">
         <v>13304</v>
@@ -5528,7 +5527,7 @@
         <v>9978</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>159</v>
       </c>
@@ -5548,7 +5547,7 @@
         <v>31460</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>308007</v>
       </c>
@@ -5556,10 +5555,10 @@
         <v>162</v>
       </c>
       <c r="C178" s="5">
-        <v>77460</v>
+        <v>78830</v>
       </c>
       <c r="D178" s="5">
-        <v>38730</v>
+        <v>39410</v>
       </c>
       <c r="E178" s="5">
         <v>110613</v>
@@ -5568,7 +5567,7 @@
         <v>82960</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>302061</v>
       </c>
@@ -5576,10 +5575,10 @@
         <v>164</v>
       </c>
       <c r="C179" s="5">
-        <v>10140</v>
+        <v>10320</v>
       </c>
       <c r="D179" s="5">
-        <v>6970</v>
+        <v>7090</v>
       </c>
       <c r="E179" s="5">
         <v>12067</v>
@@ -5588,7 +5587,7 @@
         <v>9050</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>308019</v>
       </c>
@@ -5596,10 +5595,10 @@
         <v>408</v>
       </c>
       <c r="C180" s="5">
-        <v>10740</v>
+        <v>10930</v>
       </c>
       <c r="D180" s="5">
-        <v>7380</v>
+        <v>7510</v>
       </c>
       <c r="E180" s="5">
         <v>12781</v>
@@ -5608,7 +5607,7 @@
         <v>9586</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>167</v>
       </c>
@@ -5628,7 +5627,7 @@
         <v>50873</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>169</v>
       </c>
@@ -5648,7 +5647,7 @@
         <v>60114</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>302033</v>
       </c>
@@ -5656,10 +5655,10 @@
         <v>171</v>
       </c>
       <c r="C183" s="5">
-        <v>12850</v>
+        <v>13070</v>
       </c>
       <c r="D183" s="5">
-        <v>8830</v>
+        <v>8980</v>
       </c>
       <c r="E183" s="5">
         <v>15292</v>
@@ -5668,7 +5667,7 @@
         <v>11469</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>173</v>
       </c>
@@ -5688,7 +5687,7 @@
         <v>104069</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>306087</v>
       </c>
@@ -5696,10 +5695,10 @@
         <v>482</v>
       </c>
       <c r="C185" s="5">
-        <v>158450</v>
+        <v>161250</v>
       </c>
       <c r="D185" s="5">
-        <v>79220</v>
+        <v>80620</v>
       </c>
       <c r="E185" s="5">
         <v>212125</v>
@@ -5708,7 +5707,7 @@
         <v>159094</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>303009</v>
       </c>
@@ -5716,10 +5715,10 @@
         <v>175</v>
       </c>
       <c r="C186" s="5">
-        <v>9470</v>
+        <v>9630</v>
       </c>
       <c r="D186" s="5">
-        <v>6510</v>
+        <v>6620</v>
       </c>
       <c r="E186" s="5">
         <v>11269</v>
@@ -5728,7 +5727,7 @@
         <v>8452</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>176</v>
       </c>
@@ -5748,7 +5747,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>308047</v>
       </c>
@@ -5756,10 +5755,10 @@
         <v>178</v>
       </c>
       <c r="C188" s="5">
-        <v>16550</v>
+        <v>16840</v>
       </c>
       <c r="D188" s="5">
-        <v>8270</v>
+        <v>8420</v>
       </c>
       <c r="E188" s="5">
         <v>92787</v>
@@ -5768,7 +5767,7 @@
         <v>69590</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>180</v>
       </c>
@@ -5788,7 +5787,7 @@
         <v>6310</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>181</v>
       </c>
@@ -5808,7 +5807,7 @@
         <v>11548</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>183</v>
       </c>
@@ -5828,7 +5827,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>185</v>
       </c>
@@ -5848,7 +5847,7 @@
         <v>2113514</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>188</v>
       </c>
@@ -5868,7 +5867,7 @@
         <v>76309</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>190</v>
       </c>
@@ -5888,7 +5887,7 @@
         <v>82815</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>305020</v>
       </c>
@@ -5896,10 +5895,10 @@
         <v>192</v>
       </c>
       <c r="C195" s="5">
-        <v>7420</v>
+        <v>7550</v>
       </c>
       <c r="D195" s="5">
-        <v>5100</v>
+        <v>5190</v>
       </c>
       <c r="E195" s="5">
         <v>8830</v>
@@ -5908,7 +5907,7 @@
         <v>6623</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>301025</v>
       </c>
@@ -5916,10 +5915,10 @@
         <v>194</v>
       </c>
       <c r="C196" s="5">
-        <v>8160</v>
+        <v>8300</v>
       </c>
       <c r="D196" s="5">
-        <v>5610</v>
+        <v>5700</v>
       </c>
       <c r="E196" s="5">
         <v>9710</v>
@@ -5928,7 +5927,7 @@
         <v>7283</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>301089</v>
       </c>
@@ -5936,10 +5935,10 @@
         <v>193</v>
       </c>
       <c r="C197" s="5">
-        <v>16240</v>
+        <v>16530</v>
       </c>
       <c r="D197" s="5">
-        <v>11160</v>
+        <v>11360</v>
       </c>
       <c r="E197" s="5">
         <v>19326</v>
@@ -5948,7 +5947,7 @@
         <v>14495</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>196</v>
       </c>
@@ -5968,7 +5967,7 @@
         <v>76309</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>301026</v>
       </c>
@@ -5976,10 +5975,10 @@
         <v>198</v>
       </c>
       <c r="C199" s="5">
-        <v>9700</v>
+        <v>9870</v>
       </c>
       <c r="D199" s="5">
-        <v>6670</v>
+        <v>6780</v>
       </c>
       <c r="E199" s="5">
         <v>11543</v>
@@ -5988,7 +5987,7 @@
         <v>8657</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>309015</v>
       </c>
@@ -5996,10 +5995,10 @@
         <v>208</v>
       </c>
       <c r="C200" s="5">
-        <v>3300</v>
+        <v>3360</v>
       </c>
       <c r="D200" s="5">
-        <v>2270</v>
+        <v>2310</v>
       </c>
       <c r="E200" s="5">
         <v>3927</v>
@@ -6008,7 +6007,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>205</v>
       </c>
@@ -6028,7 +6027,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>210</v>
       </c>
@@ -6048,7 +6047,7 @@
         <v>34589</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>303012</v>
       </c>
@@ -6056,10 +6055,10 @@
         <v>212</v>
       </c>
       <c r="C203" s="5">
-        <v>12100</v>
+        <v>12300</v>
       </c>
       <c r="D203" s="5">
-        <v>8320</v>
+        <v>8450</v>
       </c>
       <c r="E203" s="5">
         <v>14399</v>
@@ -6068,7 +6067,7 @@
         <v>10799</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>213</v>
       </c>
@@ -6088,7 +6087,7 @@
         <v>459872</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>301017</v>
       </c>
@@ -6096,10 +6095,10 @@
         <v>152</v>
       </c>
       <c r="C205" s="5">
-        <v>7710</v>
+        <v>7860</v>
       </c>
       <c r="D205" s="5">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="E205" s="5">
         <v>9175</v>
@@ -6108,7 +6107,7 @@
         <v>6881</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>309016</v>
       </c>
@@ -6116,10 +6115,10 @@
         <v>215</v>
       </c>
       <c r="C206" s="5">
-        <v>2260</v>
+        <v>2290</v>
       </c>
       <c r="D206" s="5">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="E206" s="5">
         <v>2689</v>
@@ -6128,7 +6127,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>303014</v>
       </c>
@@ -6136,10 +6135,10 @@
         <v>218</v>
       </c>
       <c r="C207" s="5">
-        <v>8670</v>
+        <v>8830</v>
       </c>
       <c r="D207" s="5">
-        <v>5960</v>
+        <v>6070</v>
       </c>
       <c r="E207" s="5">
         <v>10317</v>
@@ -6148,7 +6147,7 @@
         <v>7738</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>220</v>
       </c>
@@ -6168,7 +6167,7 @@
         <v>67085</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>301035</v>
       </c>
@@ -6176,10 +6175,10 @@
         <v>222</v>
       </c>
       <c r="C209" s="5">
-        <v>7680</v>
+        <v>7810</v>
       </c>
       <c r="D209" s="5">
-        <v>5280</v>
+        <v>5370</v>
       </c>
       <c r="E209" s="5">
         <v>9139</v>
@@ -6188,7 +6187,7 @@
         <v>6854</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>202215</v>
       </c>
@@ -6208,7 +6207,7 @@
         <v>49263</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>202249</v>
       </c>
@@ -6228,7 +6227,7 @@
         <v>73377</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>225</v>
       </c>
@@ -6248,7 +6247,7 @@
         <v>359855</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>301044</v>
       </c>
@@ -6256,10 +6255,10 @@
         <v>163</v>
       </c>
       <c r="C213" s="5">
-        <v>8540</v>
+        <v>8690</v>
       </c>
       <c r="D213" s="5">
-        <v>5870</v>
+        <v>5970</v>
       </c>
       <c r="E213" s="5">
         <v>10163</v>
@@ -6268,7 +6267,7 @@
         <v>7622</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>306074</v>
       </c>
@@ -6276,10 +6275,10 @@
         <v>515</v>
       </c>
       <c r="C214" s="5">
-        <v>12350</v>
+        <v>12580</v>
       </c>
       <c r="D214" s="5">
-        <v>8490</v>
+        <v>8650</v>
       </c>
       <c r="E214" s="5">
         <v>14697</v>
@@ -6288,7 +6287,7 @@
         <v>11023</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>306075</v>
       </c>
@@ -6296,10 +6295,10 @@
         <v>485</v>
       </c>
       <c r="C215" s="5">
-        <v>12100</v>
+        <v>12300</v>
       </c>
       <c r="D215" s="5">
-        <v>8320</v>
+        <v>8450</v>
       </c>
       <c r="E215" s="5">
         <v>14399</v>
@@ -6308,7 +6307,7 @@
         <v>10799</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>306080</v>
       </c>
@@ -6316,10 +6315,10 @@
         <v>483</v>
       </c>
       <c r="C216" s="5">
-        <v>12300</v>
+        <v>12530</v>
       </c>
       <c r="D216" s="5">
-        <v>8450</v>
+        <v>8610</v>
       </c>
       <c r="E216" s="5">
         <v>14637</v>
@@ -6328,7 +6327,7 @@
         <v>10978</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>306076</v>
       </c>
@@ -6336,10 +6335,10 @@
         <v>484</v>
       </c>
       <c r="C217" s="5">
-        <v>12370</v>
+        <v>12590</v>
       </c>
       <c r="D217" s="5">
-        <v>8500</v>
+        <v>8650</v>
       </c>
       <c r="E217" s="5">
         <v>14720</v>
@@ -6348,7 +6347,7 @@
         <v>11040</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>306078</v>
       </c>
@@ -6356,10 +6355,10 @@
         <v>487</v>
       </c>
       <c r="C218" s="5">
-        <v>11180</v>
+        <v>11380</v>
       </c>
       <c r="D218" s="5">
-        <v>7680</v>
+        <v>7820</v>
       </c>
       <c r="E218" s="5">
         <v>13304</v>
@@ -6368,7 +6367,7 @@
         <v>9978</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>232</v>
       </c>
@@ -6388,7 +6387,7 @@
         <v>107786</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>235</v>
       </c>
@@ -6408,7 +6407,7 @@
         <v>62867</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>236</v>
       </c>
@@ -6428,7 +6427,7 @@
         <v>123517</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>309017</v>
       </c>
@@ -6436,10 +6435,10 @@
         <v>238</v>
       </c>
       <c r="C222" s="5">
-        <v>7460</v>
+        <v>7580</v>
       </c>
       <c r="D222" s="5">
-        <v>5130</v>
+        <v>5210</v>
       </c>
       <c r="E222" s="5">
         <v>8877</v>
@@ -6448,7 +6447,7 @@
         <v>6658</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>301028</v>
       </c>
@@ -6456,10 +6455,10 @@
         <v>200</v>
       </c>
       <c r="C223" s="5">
-        <v>3420</v>
+        <v>3490</v>
       </c>
       <c r="D223" s="5">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="E223" s="5">
         <v>4070</v>
@@ -6468,7 +6467,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>303058</v>
       </c>
@@ -6476,10 +6475,10 @@
         <v>242</v>
       </c>
       <c r="C224" s="5">
-        <v>46890</v>
+        <v>47720</v>
       </c>
       <c r="D224" s="5">
-        <v>23440</v>
+        <v>23860</v>
       </c>
       <c r="E224" s="5">
         <v>66959</v>
@@ -6488,7 +6487,7 @@
         <v>50219</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>303007</v>
       </c>
@@ -6496,10 +6495,10 @@
         <v>138</v>
       </c>
       <c r="C225" s="5">
-        <v>11410</v>
+        <v>11620</v>
       </c>
       <c r="D225" s="5">
-        <v>7840</v>
+        <v>7990</v>
       </c>
       <c r="E225" s="5">
         <v>13578</v>
@@ -6508,7 +6507,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>303016</v>
       </c>
@@ -6516,10 +6515,10 @@
         <v>244</v>
       </c>
       <c r="C226" s="5">
-        <v>8880</v>
+        <v>9040</v>
       </c>
       <c r="D226" s="5">
-        <v>6100</v>
+        <v>6210</v>
       </c>
       <c r="E226" s="5">
         <v>10567</v>
@@ -6528,7 +6527,7 @@
         <v>7925</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>303018</v>
       </c>
@@ -6536,10 +6535,10 @@
         <v>376</v>
       </c>
       <c r="C227" s="5">
-        <v>13520</v>
+        <v>13760</v>
       </c>
       <c r="D227" s="5">
-        <v>9290</v>
+        <v>9460</v>
       </c>
       <c r="E227" s="5">
         <v>16089</v>
@@ -6548,7 +6547,7 @@
         <v>12067</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>303048</v>
       </c>
@@ -6556,10 +6555,10 @@
         <v>247</v>
       </c>
       <c r="C228" s="5">
-        <v>21680</v>
+        <v>22060</v>
       </c>
       <c r="D228" s="5">
-        <v>14900</v>
+        <v>15160</v>
       </c>
       <c r="E228" s="5">
         <v>25799</v>
@@ -6568,7 +6567,7 @@
         <v>19349</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>303123</v>
       </c>
@@ -6576,10 +6575,10 @@
         <v>248</v>
       </c>
       <c r="C229" s="5">
-        <v>20860</v>
+        <v>21230</v>
       </c>
       <c r="D229" s="5">
-        <v>14340</v>
+        <v>14590</v>
       </c>
       <c r="E229" s="5">
         <v>24823</v>
@@ -6588,7 +6587,7 @@
         <v>18617</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>249</v>
       </c>
@@ -6608,7 +6607,7 @@
         <v>64778</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>305025</v>
       </c>
@@ -6616,10 +6615,10 @@
         <v>251</v>
       </c>
       <c r="C231" s="5">
-        <v>15010</v>
+        <v>15280</v>
       </c>
       <c r="D231" s="5">
-        <v>10320</v>
+        <v>10500</v>
       </c>
       <c r="E231" s="5">
         <v>17862</v>
@@ -6628,7 +6627,7 @@
         <v>13397</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>305027</v>
       </c>
@@ -6636,10 +6635,10 @@
         <v>517</v>
       </c>
       <c r="C232" s="5">
-        <v>8300</v>
+        <v>8450</v>
       </c>
       <c r="D232" s="5">
-        <v>5700</v>
+        <v>5810</v>
       </c>
       <c r="E232" s="5">
         <v>9877</v>
@@ -6648,7 +6647,7 @@
         <v>7408</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>305028</v>
       </c>
@@ -6656,10 +6655,10 @@
         <v>253</v>
       </c>
       <c r="C233" s="5">
-        <v>8660</v>
+        <v>8820</v>
       </c>
       <c r="D233" s="5">
-        <v>5950</v>
+        <v>6060</v>
       </c>
       <c r="E233" s="5">
         <v>10305</v>
@@ -6668,7 +6667,7 @@
         <v>7729</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>305029</v>
       </c>
@@ -6676,10 +6675,10 @@
         <v>518</v>
       </c>
       <c r="C234" s="5">
-        <v>8510</v>
+        <v>8660</v>
       </c>
       <c r="D234" s="5">
-        <v>5850</v>
+        <v>5950</v>
       </c>
       <c r="E234" s="5">
         <v>10127</v>
@@ -6688,7 +6687,7 @@
         <v>7595</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>202260</v>
       </c>
@@ -6708,7 +6707,7 @@
         <v>108019</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>303047</v>
       </c>
@@ -6716,10 +6715,10 @@
         <v>246</v>
       </c>
       <c r="C236" s="5">
-        <v>22020</v>
+        <v>22400</v>
       </c>
       <c r="D236" s="5">
-        <v>15140</v>
+        <v>15400</v>
       </c>
       <c r="E236" s="5">
         <v>26204</v>
@@ -6728,7 +6727,7 @@
         <v>19653</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>256</v>
       </c>
@@ -6748,7 +6747,7 @@
         <v>33588</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>302039</v>
       </c>
@@ -6756,10 +6755,10 @@
         <v>203</v>
       </c>
       <c r="C238" s="5">
-        <v>10210</v>
+        <v>10380</v>
       </c>
       <c r="D238" s="5">
-        <v>7020</v>
+        <v>7130</v>
       </c>
       <c r="E238" s="5">
         <v>12150</v>
@@ -6768,7 +6767,7 @@
         <v>9113</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>302031</v>
       </c>
@@ -6776,10 +6775,10 @@
         <v>154</v>
       </c>
       <c r="C239" s="5">
-        <v>10590</v>
+        <v>10780</v>
       </c>
       <c r="D239" s="5">
-        <v>7280</v>
+        <v>7410</v>
       </c>
       <c r="E239" s="5">
         <v>12602</v>
@@ -6788,7 +6787,7 @@
         <v>9452</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>258</v>
       </c>
@@ -6808,7 +6807,7 @@
         <v>76309</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>302004</v>
       </c>
@@ -6816,10 +6815,10 @@
         <v>260</v>
       </c>
       <c r="C241" s="5">
-        <v>6580</v>
+        <v>6690</v>
       </c>
       <c r="D241" s="5">
-        <v>4520</v>
+        <v>4600</v>
       </c>
       <c r="E241" s="5">
         <v>7830</v>
@@ -6828,7 +6827,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>309007</v>
       </c>
@@ -6836,10 +6835,10 @@
         <v>34</v>
       </c>
       <c r="C242" s="5">
-        <v>9410</v>
+        <v>9570</v>
       </c>
       <c r="D242" s="5">
-        <v>6470</v>
+        <v>6580</v>
       </c>
       <c r="E242" s="5">
         <v>11198</v>
@@ -6848,7 +6847,7 @@
         <v>8399</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>261</v>
       </c>
@@ -6868,7 +6867,7 @@
         <v>67085</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>305089</v>
       </c>
@@ -6876,10 +6875,10 @@
         <v>264</v>
       </c>
       <c r="C244" s="5">
-        <v>73760</v>
+        <v>75070</v>
       </c>
       <c r="D244" s="5">
-        <v>50710</v>
+        <v>51610</v>
       </c>
       <c r="E244" s="5">
         <v>87774</v>
@@ -6888,7 +6887,7 @@
         <v>65831</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>305092</v>
       </c>
@@ -6896,10 +6895,10 @@
         <v>294</v>
       </c>
       <c r="C245" s="5">
-        <v>45820</v>
+        <v>46640</v>
       </c>
       <c r="D245" s="5">
-        <v>31500</v>
+        <v>32060</v>
       </c>
       <c r="E245" s="5">
         <v>54526</v>
@@ -6908,7 +6907,7 @@
         <v>40895</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>305091</v>
       </c>
@@ -6916,10 +6915,10 @@
         <v>265</v>
       </c>
       <c r="C246" s="5">
-        <v>47060</v>
+        <v>47890</v>
       </c>
       <c r="D246" s="5">
-        <v>32350</v>
+        <v>32920</v>
       </c>
       <c r="E246" s="5">
         <v>56001</v>
@@ -6928,7 +6927,7 @@
         <v>42001</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>302053</v>
       </c>
@@ -6936,10 +6935,10 @@
         <v>266</v>
       </c>
       <c r="C247" s="5">
-        <v>4270</v>
+        <v>4350</v>
       </c>
       <c r="D247" s="5">
-        <v>2930</v>
+        <v>2990</v>
       </c>
       <c r="E247" s="5">
         <v>5081</v>
@@ -6948,7 +6947,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>267</v>
       </c>
@@ -6968,7 +6967,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>269</v>
       </c>
@@ -6988,7 +6987,7 @@
         <v>67353</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>302055</v>
       </c>
@@ -6996,10 +6995,10 @@
         <v>271</v>
       </c>
       <c r="C250" s="5">
-        <v>4700</v>
+        <v>4780</v>
       </c>
       <c r="D250" s="5">
-        <v>3230</v>
+        <v>3280</v>
       </c>
       <c r="E250" s="5">
         <v>5593</v>
@@ -7008,7 +7007,7 @@
         <v>4195</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>272</v>
       </c>
@@ -7028,7 +7027,7 @@
         <v>2985</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>302056</v>
       </c>
@@ -7036,10 +7035,10 @@
         <v>274</v>
       </c>
       <c r="C252" s="5">
-        <v>5140</v>
+        <v>5230</v>
       </c>
       <c r="D252" s="5">
-        <v>3530</v>
+        <v>3590</v>
       </c>
       <c r="E252" s="5">
         <v>6117</v>
@@ -7048,7 +7047,7 @@
         <v>4588</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>275</v>
       </c>
@@ -7068,7 +7067,7 @@
         <v>121586</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>277</v>
       </c>
@@ -7088,7 +7087,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>279</v>
       </c>
@@ -7108,7 +7107,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
         <v>281</v>
       </c>
@@ -7128,7 +7127,7 @@
         <v>108698</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>303050</v>
       </c>
@@ -7136,10 +7135,10 @@
         <v>283</v>
       </c>
       <c r="C257" s="5">
-        <v>68340</v>
+        <v>69550</v>
       </c>
       <c r="D257" s="5">
-        <v>46980</v>
+        <v>47810</v>
       </c>
       <c r="E257" s="5">
         <v>81325</v>
@@ -7148,7 +7147,7 @@
         <v>60994</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>306070</v>
       </c>
@@ -7156,10 +7155,10 @@
         <v>61</v>
       </c>
       <c r="C258" s="5">
-        <v>9010</v>
+        <v>9170</v>
       </c>
       <c r="D258" s="5">
-        <v>6190</v>
+        <v>6300</v>
       </c>
       <c r="E258" s="5">
         <v>10722</v>
@@ -7168,7 +7167,7 @@
         <v>8042</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>305107</v>
       </c>
@@ -7176,10 +7175,10 @@
         <v>46</v>
       </c>
       <c r="C259" s="5">
-        <v>39760</v>
+        <v>40460</v>
       </c>
       <c r="D259" s="5">
-        <v>19880</v>
+        <v>20230</v>
       </c>
       <c r="E259" s="5">
         <v>53229</v>
@@ -7188,7 +7187,7 @@
         <v>39922</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>306036</v>
       </c>
@@ -7196,10 +7195,10 @@
         <v>285</v>
       </c>
       <c r="C260" s="5">
-        <v>3860</v>
+        <v>3920</v>
       </c>
       <c r="D260" s="5">
-        <v>2650</v>
+        <v>2690</v>
       </c>
       <c r="E260" s="5">
         <v>4593</v>
@@ -7208,7 +7207,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
         <v>286</v>
       </c>
@@ -7228,7 +7227,7 @@
         <v>134134</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>288</v>
       </c>
@@ -7248,7 +7247,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
         <v>290</v>
       </c>
@@ -7268,7 +7267,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>292</v>
       </c>
@@ -7288,7 +7287,7 @@
         <v>74020</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>306037</v>
       </c>
@@ -7296,10 +7295,10 @@
         <v>519</v>
       </c>
       <c r="C265" s="5">
-        <v>8420</v>
+        <v>8560</v>
       </c>
       <c r="D265" s="5">
-        <v>5790</v>
+        <v>5880</v>
       </c>
       <c r="E265" s="5">
         <v>10020</v>
@@ -7308,7 +7307,7 @@
         <v>7515</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>296</v>
       </c>
@@ -7328,7 +7327,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>309020</v>
       </c>
@@ -7336,10 +7335,10 @@
         <v>298</v>
       </c>
       <c r="C267" s="5">
-        <v>1380</v>
+        <v>1410</v>
       </c>
       <c r="D267" s="5">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="E267" s="5">
         <v>1642</v>
@@ -7348,7 +7347,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
         <v>301</v>
       </c>
@@ -7368,7 +7367,7 @@
         <v>12137</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>309025</v>
       </c>
@@ -7376,10 +7375,10 @@
         <v>304</v>
       </c>
       <c r="C269" s="5">
-        <v>3060</v>
+        <v>3100</v>
       </c>
       <c r="D269" s="5">
-        <v>2100</v>
+        <v>2130</v>
       </c>
       <c r="E269" s="5">
         <v>3641</v>
@@ -7388,7 +7387,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>202258</v>
       </c>
@@ -7408,7 +7407,7 @@
         <v>23541</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>202258</v>
       </c>
@@ -7428,7 +7427,7 @@
         <v>23541</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>307</v>
       </c>
@@ -7448,7 +7447,7 @@
         <v>144001</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>202329</v>
       </c>
@@ -7468,7 +7467,7 @@
         <v>98099</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
         <v>310</v>
       </c>
@@ -7488,7 +7487,7 @@
         <v>54947</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
         <v>312</v>
       </c>
@@ -7508,7 +7507,7 @@
         <v>83262</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
         <v>314</v>
       </c>
@@ -7528,7 +7527,7 @@
         <v>141713</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
         <v>316</v>
       </c>
@@ -7548,7 +7547,7 @@
         <v>107858</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
         <v>318</v>
       </c>
@@ -7568,7 +7567,7 @@
         <v>43955</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>202216</v>
       </c>
@@ -7588,7 +7587,7 @@
         <v>39307</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
         <v>321</v>
       </c>
@@ -7608,7 +7607,7 @@
         <v>157211</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>202319</v>
       </c>
@@ -7628,7 +7627,7 @@
         <v>174407</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
         <v>324</v>
       </c>
@@ -7648,7 +7647,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
         <v>326</v>
       </c>
@@ -7668,7 +7667,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
         <v>328</v>
       </c>
@@ -7688,7 +7687,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
         <v>330</v>
       </c>
@@ -7708,7 +7707,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
         <v>332</v>
       </c>
@@ -7728,7 +7727,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
         <v>334</v>
       </c>
@@ -7748,7 +7747,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
         <v>336</v>
       </c>
@@ -7768,7 +7767,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
         <v>338</v>
       </c>
@@ -7788,7 +7787,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
         <v>340</v>
       </c>
@@ -7808,7 +7807,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
         <v>342</v>
       </c>
@@ -7828,7 +7827,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
         <v>344</v>
       </c>
@@ -7848,7 +7847,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
         <v>346</v>
       </c>
@@ -7868,7 +7867,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
         <v>348</v>
       </c>
@@ -7888,7 +7887,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
         <v>350</v>
       </c>
@@ -7908,7 +7907,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
         <v>352</v>
       </c>
@@ -7928,7 +7927,7 @@
         <v>875344</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
         <v>354</v>
       </c>
@@ -7948,7 +7947,7 @@
         <v>95582</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
         <v>356</v>
       </c>
@@ -7968,7 +7967,7 @@
         <v>130792</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
         <v>358</v>
       </c>
@@ -7988,7 +7987,7 @@
         <v>367362</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
         <v>360</v>
       </c>
@@ -8008,7 +8007,7 @@
         <v>295080</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
         <v>362</v>
       </c>
@@ -8028,7 +8027,7 @@
         <v>76755</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
         <v>363</v>
       </c>
@@ -8048,7 +8047,7 @@
         <v>109412</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
         <v>364</v>
       </c>
@@ -8068,7 +8067,7 @@
         <v>115562</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
         <v>366</v>
       </c>
@@ -8088,7 +8087,7 @@
         <v>71231</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
         <v>368</v>
       </c>
@@ -8108,7 +8107,7 @@
         <v>138763</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>202313</v>
       </c>
@@ -8128,7 +8127,7 @@
         <v>113310</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
         <v>371</v>
       </c>
@@ -8148,7 +8147,7 @@
         <v>141641</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>202315</v>
       </c>
@@ -8168,7 +8167,7 @@
         <v>57808</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>306122</v>
       </c>
@@ -8176,10 +8175,10 @@
         <v>375</v>
       </c>
       <c r="C309" s="5">
-        <v>86470</v>
+        <v>88000</v>
       </c>
       <c r="D309" s="5">
-        <v>43230</v>
+        <v>44000</v>
       </c>
       <c r="E309" s="5">
         <v>115762</v>
@@ -8188,7 +8187,7 @@
         <v>86822</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>202326</v>
       </c>
@@ -8208,7 +8207,7 @@
         <v>98099</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
         <v>377</v>
       </c>
@@ -8228,7 +8227,7 @@
         <v>444812</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>303052</v>
       </c>
@@ -8236,10 +8235,10 @@
         <v>379</v>
       </c>
       <c r="C312" s="5">
-        <v>45500</v>
+        <v>46310</v>
       </c>
       <c r="D312" s="5">
-        <v>22750</v>
+        <v>23150</v>
       </c>
       <c r="E312" s="5">
         <v>60913</v>
@@ -8248,7 +8247,7 @@
         <v>45685</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>305099</v>
       </c>
@@ -8256,10 +8255,10 @@
         <v>522</v>
       </c>
       <c r="C313" s="5">
-        <v>38150</v>
+        <v>38830</v>
       </c>
       <c r="D313" s="5">
-        <v>19070</v>
+        <v>19410</v>
       </c>
       <c r="E313" s="5">
         <v>51073</v>
@@ -8268,7 +8267,7 @@
         <v>38305</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>303055</v>
       </c>
@@ -8276,10 +8275,10 @@
         <v>300</v>
       </c>
       <c r="C314" s="5">
-        <v>53840</v>
+        <v>54790</v>
       </c>
       <c r="D314" s="5">
-        <v>26920</v>
+        <v>27390</v>
       </c>
       <c r="E314" s="5">
         <v>76884</v>
@@ -8288,7 +8287,7 @@
         <v>57663</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
         <v>383</v>
       </c>
@@ -8308,7 +8307,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
         <v>385</v>
       </c>
@@ -8328,7 +8327,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>302084</v>
       </c>
@@ -8336,10 +8335,10 @@
         <v>387</v>
       </c>
       <c r="C317" s="5">
-        <v>64800</v>
+        <v>65950</v>
       </c>
       <c r="D317" s="5">
-        <v>32400</v>
+        <v>32970</v>
       </c>
       <c r="E317" s="5">
         <v>86751</v>
@@ -8348,7 +8347,7 @@
         <v>65063</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>309027</v>
       </c>
@@ -8356,10 +8355,10 @@
         <v>388</v>
       </c>
       <c r="C318" s="5">
-        <v>4180</v>
+        <v>4260</v>
       </c>
       <c r="D318" s="5">
-        <v>2870</v>
+        <v>2930</v>
       </c>
       <c r="E318" s="5">
         <v>4974</v>
@@ -8368,7 +8367,7 @@
         <v>3731</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
         <v>389</v>
       </c>
@@ -8388,7 +8387,7 @@
         <v>96953</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
         <v>391</v>
       </c>
@@ -8408,7 +8407,7 @@
         <v>96953</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
         <v>393</v>
       </c>
@@ -8428,7 +8427,7 @@
         <v>450542</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>302085</v>
       </c>
@@ -8436,10 +8435,10 @@
         <v>395</v>
       </c>
       <c r="C322" s="5">
-        <v>30630</v>
+        <v>31170</v>
       </c>
       <c r="D322" s="5">
-        <v>15310</v>
+        <v>15580</v>
       </c>
       <c r="E322" s="5">
         <v>43740</v>
@@ -8448,7 +8447,7 @@
         <v>32805</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>301096</v>
       </c>
@@ -8456,10 +8455,10 @@
         <v>396</v>
       </c>
       <c r="C323" s="5">
-        <v>43940</v>
+        <v>44720</v>
       </c>
       <c r="D323" s="5">
-        <v>21970</v>
+        <v>22360</v>
       </c>
       <c r="E323" s="5">
         <v>62746</v>
@@ -8468,7 +8467,7 @@
         <v>47060</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>303019</v>
       </c>
@@ -8476,10 +8475,10 @@
         <v>397</v>
       </c>
       <c r="C324" s="5">
-        <v>8400</v>
+        <v>8540</v>
       </c>
       <c r="D324" s="5">
-        <v>5770</v>
+        <v>5870</v>
       </c>
       <c r="E324" s="5">
         <v>9996</v>
@@ -8488,7 +8487,7 @@
         <v>7497</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>303020</v>
       </c>
@@ -8496,10 +8495,10 @@
         <v>398</v>
       </c>
       <c r="C325" s="5">
-        <v>8860</v>
+        <v>9020</v>
       </c>
       <c r="D325" s="5">
-        <v>6090</v>
+        <v>6200</v>
       </c>
       <c r="E325" s="5">
         <v>10543</v>
@@ -8508,7 +8507,7 @@
         <v>7907</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>202424</v>
       </c>
@@ -8528,7 +8527,7 @@
         <v>28439</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>202338</v>
       </c>
@@ -8548,7 +8547,7 @@
         <v>138763</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>301093</v>
       </c>
@@ -8556,10 +8555,10 @@
         <v>424</v>
       </c>
       <c r="C328" s="5">
-        <v>37460</v>
+        <v>38110</v>
       </c>
       <c r="D328" s="5">
-        <v>25750</v>
+        <v>26200</v>
       </c>
       <c r="E328" s="5">
         <v>44577</v>
@@ -8568,7 +8567,7 @@
         <v>33433</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>301092</v>
       </c>
@@ -8576,10 +8575,10 @@
         <v>403</v>
       </c>
       <c r="C329" s="5">
-        <v>59470</v>
+        <v>60530</v>
       </c>
       <c r="D329" s="5">
-        <v>40880</v>
+        <v>41610</v>
       </c>
       <c r="E329" s="5">
         <v>70769</v>
@@ -8588,7 +8587,7 @@
         <v>53077</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>309028</v>
       </c>
@@ -8596,10 +8595,10 @@
         <v>399</v>
       </c>
       <c r="C330" s="5">
-        <v>2880</v>
+        <v>2930</v>
       </c>
       <c r="D330" s="5">
-        <v>1980</v>
+        <v>2010</v>
       </c>
       <c r="E330" s="5">
         <v>3427</v>
@@ -8608,7 +8607,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>306082</v>
       </c>
@@ -8616,10 +8615,10 @@
         <v>412</v>
       </c>
       <c r="C331" s="5">
-        <v>25150</v>
+        <v>25600</v>
       </c>
       <c r="D331" s="5">
-        <v>12570</v>
+        <v>12800</v>
       </c>
       <c r="E331" s="5">
         <v>33670</v>
@@ -8628,7 +8627,7 @@
         <v>25253</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>202347</v>
       </c>
@@ -8648,7 +8647,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>303046</v>
       </c>
@@ -8656,10 +8655,10 @@
         <v>427</v>
       </c>
       <c r="C333" s="5">
-        <v>20430</v>
+        <v>20800</v>
       </c>
       <c r="D333" s="5">
-        <v>14040</v>
+        <v>14300</v>
       </c>
       <c r="E333" s="5">
         <v>24312</v>
@@ -8668,7 +8667,7 @@
         <v>18234</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>306099</v>
       </c>
@@ -8676,10 +8675,10 @@
         <v>428</v>
       </c>
       <c r="C334" s="5">
-        <v>15540</v>
+        <v>15820</v>
       </c>
       <c r="D334" s="5">
-        <v>7770</v>
+        <v>7910</v>
       </c>
       <c r="E334" s="5">
         <v>20804</v>
@@ -8688,7 +8687,7 @@
         <v>15603</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
         <v>430</v>
       </c>
@@ -8708,7 +8707,7 @@
         <v>67085</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>432</v>
       </c>
@@ -8728,7 +8727,7 @@
         <v>110182</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
         <v>434</v>
       </c>
@@ -8748,7 +8747,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
         <v>438</v>
       </c>
@@ -8768,7 +8767,7 @@
         <v>274649</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
         <v>440</v>
       </c>
@@ -8788,7 +8787,7 @@
         <v>66138</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>303023</v>
       </c>
@@ -8796,10 +8795,10 @@
         <v>443</v>
       </c>
       <c r="C340" s="5">
-        <v>10530</v>
+        <v>10720</v>
       </c>
       <c r="D340" s="5">
-        <v>7240</v>
+        <v>7370</v>
       </c>
       <c r="E340" s="5">
         <v>12531</v>
@@ -8808,7 +8807,7 @@
         <v>9398</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>303022</v>
       </c>
@@ -8816,10 +8815,10 @@
         <v>442</v>
       </c>
       <c r="C341" s="5">
-        <v>9220</v>
+        <v>9380</v>
       </c>
       <c r="D341" s="5">
-        <v>6340</v>
+        <v>6450</v>
       </c>
       <c r="E341" s="5">
         <v>10972</v>
@@ -8828,7 +8827,7 @@
         <v>8229</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>305118</v>
       </c>
@@ -8836,10 +8835,10 @@
         <v>239</v>
       </c>
       <c r="C342" s="5">
-        <v>91530</v>
+        <v>93150</v>
       </c>
       <c r="D342" s="5">
-        <v>45760</v>
+        <v>46570</v>
       </c>
       <c r="E342" s="5">
         <v>122536</v>
@@ -8848,7 +8847,7 @@
         <v>91902</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>305121</v>
       </c>
@@ -8856,10 +8855,10 @@
         <v>240</v>
       </c>
       <c r="C343" s="5">
-        <v>162010</v>
+        <v>164880</v>
       </c>
       <c r="D343" s="5">
-        <v>81000</v>
+        <v>82440</v>
       </c>
       <c r="E343" s="5">
         <v>216891</v>
@@ -8868,7 +8867,7 @@
         <v>162668</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>303025</v>
       </c>
@@ -8876,10 +8875,10 @@
         <v>449</v>
       </c>
       <c r="C344" s="5">
-        <v>11410</v>
+        <v>11620</v>
       </c>
       <c r="D344" s="5">
-        <v>7840</v>
+        <v>7990</v>
       </c>
       <c r="E344" s="5">
         <v>13578</v>
@@ -8888,7 +8887,7 @@
         <v>10184</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>202335</v>
       </c>
@@ -8908,7 +8907,7 @@
         <v>83065</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>301082</v>
       </c>
@@ -8916,10 +8915,10 @@
         <v>455</v>
       </c>
       <c r="C346" s="5">
-        <v>8860</v>
+        <v>9020</v>
       </c>
       <c r="D346" s="5">
-        <v>6090</v>
+        <v>6200</v>
       </c>
       <c r="E346" s="5">
         <v>10543</v>
@@ -8928,7 +8927,7 @@
         <v>7907</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>305181</v>
       </c>
@@ -8936,10 +8935,10 @@
         <v>523</v>
       </c>
       <c r="C347" s="5">
-        <v>19570</v>
+        <v>19920</v>
       </c>
       <c r="D347" s="5">
-        <v>13450</v>
+        <v>13690</v>
       </c>
       <c r="E347" s="5">
         <v>23288</v>
@@ -8948,7 +8947,7 @@
         <v>17466</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>457</v>
       </c>
@@ -8968,7 +8967,7 @@
         <v>78597</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
         <v>459</v>
       </c>
@@ -8988,7 +8987,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>202344</v>
       </c>
@@ -9008,7 +9007,7 @@
         <v>101423</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>303057</v>
       </c>
@@ -9016,10 +9015,10 @@
         <v>464</v>
       </c>
       <c r="C351" s="5">
-        <v>21310</v>
+        <v>21690</v>
       </c>
       <c r="D351" s="5">
-        <v>10650</v>
+        <v>10840</v>
       </c>
       <c r="E351" s="5">
         <v>28529</v>
@@ -9028,7 +9027,7 @@
         <v>21397</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>302027</v>
       </c>
@@ -9036,10 +9035,10 @@
         <v>466</v>
       </c>
       <c r="C352" s="5">
-        <v>18320</v>
+        <v>18640</v>
       </c>
       <c r="D352" s="5">
-        <v>12590</v>
+        <v>12810</v>
       </c>
       <c r="E352" s="5">
         <v>21801</v>
@@ -9048,7 +9047,7 @@
         <v>16351</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>467</v>
       </c>
@@ -9068,7 +9067,7 @@
         <v>55502</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>469</v>
       </c>
@@ -9088,7 +9087,7 @@
         <v>55502</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
         <v>471</v>
       </c>
@@ -9108,7 +9107,7 @@
         <v>32354</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>309004</v>
       </c>
@@ -9116,10 +9115,10 @@
         <v>15</v>
       </c>
       <c r="C356" s="5">
-        <v>3570</v>
+        <v>3630</v>
       </c>
       <c r="D356" s="5">
-        <v>2450</v>
+        <v>2490</v>
       </c>
       <c r="E356" s="5">
         <v>4248</v>
@@ -9128,7 +9127,7 @@
         <v>3186</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>306042</v>
       </c>
@@ -9136,10 +9135,10 @@
         <v>474</v>
       </c>
       <c r="C357" s="5">
-        <v>4990</v>
+        <v>5090</v>
       </c>
       <c r="D357" s="5">
-        <v>3430</v>
+        <v>3500</v>
       </c>
       <c r="E357" s="5">
         <v>5938</v>
@@ -9148,7 +9147,7 @@
         <v>4454</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
         <v>478</v>
       </c>
@@ -9168,7 +9167,7 @@
         <v>109234</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>480</v>
       </c>
@@ -9188,7 +9187,7 @@
         <v>141695</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
         <v>489</v>
       </c>
@@ -9208,7 +9207,7 @@
         <v>113346</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>306111</v>
       </c>
@@ -9216,10 +9215,10 @@
         <v>245</v>
       </c>
       <c r="C361" s="5">
-        <v>77540</v>
+        <v>78910</v>
       </c>
       <c r="D361" s="5">
-        <v>38770</v>
+        <v>39450</v>
       </c>
       <c r="E361" s="5">
         <v>103807</v>
@@ -9228,7 +9227,7 @@
         <v>77855</v>
       </c>
     </row>
-    <row r="362" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>306123</v>
       </c>
@@ -9236,10 +9235,10 @@
         <v>491</v>
       </c>
       <c r="C362" s="5">
-        <v>44240</v>
+        <v>45020</v>
       </c>
       <c r="D362" s="5">
-        <v>30410</v>
+        <v>30950</v>
       </c>
       <c r="E362" s="5">
         <v>52646</v>
@@ -9248,7 +9247,7 @@
         <v>39485</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
         <v>492</v>
       </c>
@@ -9268,7 +9267,7 @@
         <v>46815</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>302080</v>
       </c>
@@ -9276,10 +9275,10 @@
         <v>495</v>
       </c>
       <c r="C364" s="5">
-        <v>83470</v>
+        <v>84940</v>
       </c>
       <c r="D364" s="5">
-        <v>57380</v>
+        <v>58390</v>
       </c>
       <c r="E364" s="5">
         <v>99329</v>
@@ -9288,7 +9287,7 @@
         <v>74497</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
         <v>496</v>
       </c>
@@ -9308,7 +9307,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
         <v>498</v>
       </c>
@@ -9328,7 +9327,7 @@
         <v>61061</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>202270</v>
       </c>
@@ -9348,7 +9347,7 @@
         <v>17231</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>202270</v>
       </c>
@@ -9368,7 +9367,7 @@
         <v>17231</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>202225</v>
       </c>
@@ -9388,7 +9387,7 @@
         <v>71557</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>309029</v>
       </c>
@@ -9396,10 +9395,10 @@
         <v>404</v>
       </c>
       <c r="C370" s="5">
-        <v>1860</v>
+        <v>1890</v>
       </c>
       <c r="D370" s="5">
-        <v>1280</v>
+        <v>1300</v>
       </c>
       <c r="E370" s="5">
         <v>2213</v>
@@ -9408,7 +9407,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>306002</v>
       </c>
@@ -9416,10 +9415,10 @@
         <v>70</v>
       </c>
       <c r="C371" s="5">
-        <v>2780</v>
+        <v>2830</v>
       </c>
       <c r="D371" s="5">
-        <v>1910</v>
+        <v>1940</v>
       </c>
       <c r="E371" s="5">
         <v>3308</v>
@@ -9428,7 +9427,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>306017</v>
       </c>
@@ -9436,10 +9435,10 @@
         <v>149</v>
       </c>
       <c r="C372" s="5">
-        <v>4340</v>
+        <v>4420</v>
       </c>
       <c r="D372" s="5">
-        <v>2980</v>
+        <v>3040</v>
       </c>
       <c r="E372" s="5">
         <v>5165</v>
@@ -9448,7 +9447,7 @@
         <v>3874</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>306018</v>
       </c>
@@ -9456,10 +9455,10 @@
         <v>150</v>
       </c>
       <c r="C373" s="5">
-        <v>7390</v>
+        <v>7520</v>
       </c>
       <c r="D373" s="5">
-        <v>5080</v>
+        <v>5170</v>
       </c>
       <c r="E373" s="5">
         <v>8794</v>
@@ -9468,7 +9467,7 @@
         <v>6596</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>306004</v>
       </c>
@@ -9476,10 +9475,10 @@
         <v>187</v>
       </c>
       <c r="C374" s="5">
-        <v>2420</v>
+        <v>2460</v>
       </c>
       <c r="D374" s="5">
-        <v>1660</v>
+        <v>1690</v>
       </c>
       <c r="E374" s="5">
         <v>2880</v>
@@ -9488,7 +9487,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>306059</v>
       </c>
@@ -9496,10 +9495,10 @@
         <v>126</v>
       </c>
       <c r="C375" s="5">
-        <v>6380</v>
+        <v>6500</v>
       </c>
       <c r="D375" s="5">
-        <v>4380</v>
+        <v>4470</v>
       </c>
       <c r="E375" s="5">
         <v>7592</v>
@@ -9508,7 +9507,7 @@
         <v>5694</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>306039</v>
       </c>
@@ -9516,10 +9515,10 @@
         <v>446</v>
       </c>
       <c r="C376" s="5">
-        <v>5730</v>
+        <v>5820</v>
       </c>
       <c r="D376" s="5">
-        <v>3940</v>
+        <v>4000</v>
       </c>
       <c r="E376" s="5">
         <v>6819</v>
@@ -9528,7 +9527,7 @@
         <v>5114</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>306170</v>
       </c>
@@ -9536,10 +9535,10 @@
         <v>62</v>
       </c>
       <c r="C377" s="5">
-        <v>8260</v>
+        <v>8400</v>
       </c>
       <c r="D377" s="5">
-        <v>5680</v>
+        <v>5770</v>
       </c>
       <c r="E377" s="5">
         <v>9829</v>
@@ -9548,7 +9547,7 @@
         <v>7372</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>306098</v>
       </c>
@@ -9556,10 +9555,10 @@
         <v>452</v>
       </c>
       <c r="C378" s="5">
-        <v>19520</v>
+        <v>19870</v>
       </c>
       <c r="D378" s="5">
-        <v>9760</v>
+        <v>9930</v>
       </c>
       <c r="E378" s="5">
         <v>26132</v>
@@ -9568,7 +9567,7 @@
         <v>19599</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>301007</v>
       </c>
@@ -9576,10 +9575,10 @@
         <v>41</v>
       </c>
       <c r="C379" s="5">
-        <v>8450</v>
+        <v>8590</v>
       </c>
       <c r="D379" s="5">
-        <v>5810</v>
+        <v>5900</v>
       </c>
       <c r="E379" s="5">
         <v>10056</v>
@@ -9588,7 +9587,7 @@
         <v>7542</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>301014</v>
       </c>
@@ -9596,10 +9595,10 @@
         <v>409</v>
       </c>
       <c r="C380" s="5">
-        <v>2260</v>
+        <v>2290</v>
       </c>
       <c r="D380" s="5">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="E380" s="5">
         <v>2689</v>
@@ -9608,7 +9607,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>702207</v>
       </c>
@@ -9616,10 +9615,10 @@
         <v>157</v>
       </c>
       <c r="C381" s="5">
-        <v>4020</v>
+        <v>4090</v>
       </c>
       <c r="D381" s="5">
-        <v>2010</v>
+        <v>2040</v>
       </c>
       <c r="E381" s="5">
         <v>5382</v>
@@ -9628,7 +9627,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>305035</v>
       </c>
@@ -9636,10 +9635,10 @@
         <v>158</v>
       </c>
       <c r="C382" s="5">
-        <v>4290</v>
+        <v>4370</v>
       </c>
       <c r="D382" s="5">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="E382" s="5">
         <v>5105</v>
@@ -9648,7 +9647,7 @@
         <v>3829</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>301095</v>
       </c>
@@ -9656,10 +9655,10 @@
         <v>161</v>
       </c>
       <c r="C383" s="5">
-        <v>19310</v>
+        <v>19650</v>
       </c>
       <c r="D383" s="5">
-        <v>13270</v>
+        <v>13510</v>
       </c>
       <c r="E383" s="5">
         <v>22979</v>
@@ -9668,7 +9667,7 @@
         <v>17234</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>301021</v>
       </c>
@@ -9676,10 +9675,10 @@
         <v>199</v>
       </c>
       <c r="C384" s="5">
-        <v>4110</v>
+        <v>4190</v>
       </c>
       <c r="D384" s="5">
-        <v>2820</v>
+        <v>2880</v>
       </c>
       <c r="E384" s="5">
         <v>4891</v>
@@ -9688,7 +9687,7 @@
         <v>3668</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>301034</v>
       </c>
@@ -9696,10 +9695,10 @@
         <v>113</v>
       </c>
       <c r="C385" s="5">
-        <v>4030</v>
+        <v>4100</v>
       </c>
       <c r="D385" s="5">
-        <v>2770</v>
+        <v>2820</v>
       </c>
       <c r="E385" s="5">
         <v>4796</v>
@@ -9708,7 +9707,7 @@
         <v>3597</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>307011</v>
       </c>
@@ -9716,10 +9715,10 @@
         <v>476</v>
       </c>
       <c r="C386" s="5">
-        <v>1420</v>
+        <v>1460</v>
       </c>
       <c r="D386" s="5">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="E386" s="5">
         <v>1690</v>
@@ -9728,7 +9727,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>307012</v>
       </c>
@@ -9736,10 +9735,10 @@
         <v>477</v>
       </c>
       <c r="C387" s="5">
-        <v>1310</v>
+        <v>1330</v>
       </c>
       <c r="D387" s="5">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="E387" s="5">
         <v>1559</v>
@@ -9748,7 +9747,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>222222222</v>
       </c>
@@ -9769,7 +9768,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F387" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F388"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
